--- a/学生成绩模板_副本.xlsx
+++ b/学生成绩模板_副本.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kin9/python_code/score analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF8EED9-BF88-5D4E-92C4-4176BFA95C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6B441C-A32F-7843-BEAA-6F551A2BFF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4440" yWindow="920" windowWidth="24960" windowHeight="16900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,9 +185,6 @@
     <t>邱睿</t>
   </si>
   <si>
-    <t>李果</t>
-  </si>
-  <si>
     <t>总分_考试1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -353,6 +350,10 @@
   </si>
   <si>
     <t>生物集团排名_考试2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李昀珊</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -758,130 +759,130 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:43">
@@ -2349,7 +2350,7 @@
     </row>
     <row r="13" spans="1:43">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="B13" s="2">
         <f t="shared" si="0"/>

--- a/学生成绩模板_副本.xlsx
+++ b/学生成绩模板_副本.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kin9/python_code/score analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6B441C-A32F-7843-BEAA-6F551A2BFF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99947D74-E103-1A44-B1A4-AA2A8E5314BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4440" yWindow="920" windowWidth="24960" windowHeight="16900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="93">
   <si>
     <t>姓名</t>
   </si>
@@ -438,7 +439,17 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -747,14 +758,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ51"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="43" width="14" customWidth="1"/>
+    <col min="2" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="21.33203125" customWidth="1"/>
+    <col min="17" max="22" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,71 +834,8 @@
       <c r="V1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:43">
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -953,77 +903,13 @@
       <c r="V2">
         <v>912</v>
       </c>
-      <c r="W2" s="2">
-        <f>SUM(Z2,AC2,AF2,AI2,AL2,AO2)</f>
-        <v>575</v>
-      </c>
-      <c r="X2">
-        <v>321</v>
-      </c>
-      <c r="Y2">
-        <v>1158</v>
-      </c>
-      <c r="Z2">
-        <v>108</v>
-      </c>
-      <c r="AA2">
-        <v>91</v>
-      </c>
-      <c r="AB2">
-        <v>485</v>
-      </c>
-      <c r="AC2">
-        <v>126</v>
-      </c>
-      <c r="AD2">
-        <v>4</v>
-      </c>
-      <c r="AE2">
-        <v>60</v>
-      </c>
-      <c r="AF2">
-        <v>120</v>
-      </c>
-      <c r="AG2">
-        <v>73</v>
-      </c>
-      <c r="AH2">
-        <v>350</v>
-      </c>
-      <c r="AI2">
-        <v>90</v>
-      </c>
-      <c r="AJ2">
-        <v>2</v>
-      </c>
-      <c r="AK2">
-        <v>63</v>
-      </c>
-      <c r="AL2">
-        <v>79</v>
-      </c>
-      <c r="AM2">
-        <v>60</v>
-      </c>
-      <c r="AN2">
-        <v>395</v>
-      </c>
-      <c r="AO2">
-        <v>52</v>
-      </c>
-      <c r="AP2">
-        <v>192</v>
-      </c>
-      <c r="AQ2">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="3" spans="1:43">
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="2">
-        <f t="shared" ref="B3:B50" si="0">SUM(E3,H3,K3,N3,Q3,T3)</f>
+        <f>SUM(E3,H3,K3,N3,Q3,T3)</f>
         <v>568</v>
       </c>
       <c r="C3">
@@ -1086,77 +972,13 @@
       <c r="V3">
         <v>825</v>
       </c>
-      <c r="W3" s="2">
-        <f t="shared" ref="W3:W50" si="1">SUM(Z3,AC3,AF3,AI3,AL3,AO3)</f>
-        <v>568</v>
-      </c>
-      <c r="X3">
-        <v>7</v>
-      </c>
-      <c r="Y3">
-        <v>279</v>
-      </c>
-      <c r="Z3">
-        <v>107</v>
-      </c>
-      <c r="AA3">
-        <v>117</v>
-      </c>
-      <c r="AB3">
-        <v>559</v>
-      </c>
-      <c r="AC3">
-        <v>118</v>
-      </c>
-      <c r="AD3">
-        <v>37</v>
-      </c>
-      <c r="AE3">
-        <v>182</v>
-      </c>
-      <c r="AF3">
-        <v>127</v>
-      </c>
-      <c r="AG3">
-        <v>12</v>
-      </c>
-      <c r="AH3">
-        <v>126</v>
-      </c>
-      <c r="AI3">
-        <v>81</v>
-      </c>
-      <c r="AJ3">
-        <v>32</v>
-      </c>
-      <c r="AK3">
-        <v>284</v>
-      </c>
-      <c r="AL3">
-        <v>80</v>
-      </c>
-      <c r="AM3">
-        <v>60</v>
-      </c>
-      <c r="AN3">
-        <v>395</v>
-      </c>
-      <c r="AO3">
-        <v>55</v>
-      </c>
-      <c r="AP3">
-        <v>151</v>
-      </c>
-      <c r="AQ3">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="4" spans="1:43">
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E4,H4,K4,N4,Q4,T4)</f>
         <v>588</v>
       </c>
       <c r="C4">
@@ -1219,77 +1041,13 @@
       <c r="V4">
         <v>424</v>
       </c>
-      <c r="W4" s="2">
-        <f t="shared" si="1"/>
-        <v>588</v>
-      </c>
-      <c r="X4">
-        <v>5</v>
-      </c>
-      <c r="Y4">
-        <v>219</v>
-      </c>
-      <c r="Z4">
-        <v>104</v>
-      </c>
-      <c r="AA4">
-        <v>224</v>
-      </c>
-      <c r="AB4">
-        <v>808</v>
-      </c>
-      <c r="AC4">
-        <v>142</v>
-      </c>
-      <c r="AD4">
-        <v>1</v>
-      </c>
-      <c r="AE4">
-        <v>3</v>
-      </c>
-      <c r="AF4">
-        <v>101</v>
-      </c>
-      <c r="AG4">
-        <v>331</v>
-      </c>
-      <c r="AH4">
-        <v>1095</v>
-      </c>
-      <c r="AI4">
-        <v>84</v>
-      </c>
-      <c r="AJ4">
-        <v>14</v>
-      </c>
-      <c r="AK4">
-        <v>185</v>
-      </c>
-      <c r="AL4">
-        <v>90</v>
-      </c>
-      <c r="AM4">
-        <v>7</v>
-      </c>
-      <c r="AN4">
-        <v>58</v>
-      </c>
-      <c r="AO4">
-        <v>67</v>
-      </c>
-      <c r="AP4">
-        <v>37</v>
-      </c>
-      <c r="AQ4">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="5" spans="1:43">
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E5,H5,K5,N5,Q5,T5)</f>
         <v>557</v>
       </c>
       <c r="C5">
@@ -1352,77 +1110,13 @@
       <c r="V5">
         <v>578</v>
       </c>
-      <c r="W5" s="2">
-        <f t="shared" si="1"/>
-        <v>557</v>
-      </c>
-      <c r="X5">
-        <v>18</v>
-      </c>
-      <c r="Y5">
-        <v>394</v>
-      </c>
-      <c r="Z5">
-        <v>102</v>
-      </c>
-      <c r="AA5">
-        <v>306</v>
-      </c>
-      <c r="AB5">
-        <v>979</v>
-      </c>
-      <c r="AC5">
-        <v>117</v>
-      </c>
-      <c r="AD5">
-        <v>41</v>
-      </c>
-      <c r="AE5">
-        <v>197</v>
-      </c>
-      <c r="AF5">
-        <v>111</v>
-      </c>
-      <c r="AG5">
-        <v>167</v>
-      </c>
-      <c r="AH5">
-        <v>707</v>
-      </c>
-      <c r="AI5">
-        <v>90</v>
-      </c>
-      <c r="AJ5">
-        <v>2</v>
-      </c>
-      <c r="AK5">
-        <v>63</v>
-      </c>
-      <c r="AL5">
-        <v>75</v>
-      </c>
-      <c r="AM5">
-        <v>129</v>
-      </c>
-      <c r="AN5">
-        <v>638</v>
-      </c>
-      <c r="AO5">
-        <v>62</v>
-      </c>
-      <c r="AP5">
-        <v>73</v>
-      </c>
-      <c r="AQ5">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="6" spans="1:43">
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E6,H6,K6,N6,Q6,T6)</f>
         <v>559</v>
       </c>
       <c r="C6">
@@ -1485,77 +1179,13 @@
       <c r="V6">
         <v>501</v>
       </c>
-      <c r="W6" s="2">
-        <f t="shared" si="1"/>
-        <v>559</v>
-      </c>
-      <c r="X6">
-        <v>37</v>
-      </c>
-      <c r="Y6">
-        <v>494</v>
-      </c>
-      <c r="Z6">
-        <v>104</v>
-      </c>
-      <c r="AA6">
-        <v>224</v>
-      </c>
-      <c r="AB6">
-        <v>808</v>
-      </c>
-      <c r="AC6">
-        <v>110</v>
-      </c>
-      <c r="AD6">
-        <v>104</v>
-      </c>
-      <c r="AE6">
-        <v>363</v>
-      </c>
-      <c r="AF6">
-        <v>124</v>
-      </c>
-      <c r="AG6">
-        <v>29</v>
-      </c>
-      <c r="AH6">
-        <v>200</v>
-      </c>
-      <c r="AI6">
-        <v>82</v>
-      </c>
-      <c r="AJ6">
-        <v>22</v>
-      </c>
-      <c r="AK6">
-        <v>248</v>
-      </c>
-      <c r="AL6">
-        <v>74</v>
-      </c>
-      <c r="AM6">
-        <v>141</v>
-      </c>
-      <c r="AN6">
-        <v>675</v>
-      </c>
-      <c r="AO6">
-        <v>65</v>
-      </c>
-      <c r="AP6">
-        <v>54</v>
-      </c>
-      <c r="AQ6">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="7" spans="1:43">
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E7,H7,K7,N7,Q7,T7)</f>
         <v>547</v>
       </c>
       <c r="C7">
@@ -1618,77 +1248,13 @@
       <c r="V7">
         <v>825</v>
       </c>
-      <c r="W7" s="2">
-        <f t="shared" si="1"/>
-        <v>547</v>
-      </c>
-      <c r="X7">
-        <v>22</v>
-      </c>
-      <c r="Y7">
-        <v>414</v>
-      </c>
-      <c r="Z7">
-        <v>100</v>
-      </c>
-      <c r="AA7">
-        <v>367</v>
-      </c>
-      <c r="AB7">
-        <v>1104</v>
-      </c>
-      <c r="AC7">
-        <v>119</v>
-      </c>
-      <c r="AD7">
-        <v>29</v>
-      </c>
-      <c r="AE7">
-        <v>159</v>
-      </c>
-      <c r="AF7">
-        <v>122</v>
-      </c>
-      <c r="AG7">
-        <v>44</v>
-      </c>
-      <c r="AH7">
-        <v>268</v>
-      </c>
-      <c r="AI7">
-        <v>77</v>
-      </c>
-      <c r="AJ7">
-        <v>55</v>
-      </c>
-      <c r="AK7">
-        <v>405</v>
-      </c>
-      <c r="AL7">
-        <v>73</v>
-      </c>
-      <c r="AM7">
-        <v>141</v>
-      </c>
-      <c r="AN7">
-        <v>675</v>
-      </c>
-      <c r="AO7">
-        <v>56</v>
-      </c>
-      <c r="AP7">
-        <v>151</v>
-      </c>
-      <c r="AQ7">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="8" spans="1:43">
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" t="s">
         <v>41</v>
       </c>
       <c r="B8" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E8,H8,K8,N8,Q8,T8)</f>
         <v>544</v>
       </c>
       <c r="C8">
@@ -1751,77 +1317,13 @@
       <c r="V8">
         <v>424</v>
       </c>
-      <c r="W8" s="2">
-        <f t="shared" si="1"/>
-        <v>544</v>
-      </c>
-      <c r="X8">
-        <v>18</v>
-      </c>
-      <c r="Y8">
-        <v>394</v>
-      </c>
-      <c r="Z8">
-        <v>108</v>
-      </c>
-      <c r="AA8">
-        <v>91</v>
-      </c>
-      <c r="AB8">
-        <v>485</v>
-      </c>
-      <c r="AC8">
-        <v>119</v>
-      </c>
-      <c r="AD8">
-        <v>29</v>
-      </c>
-      <c r="AE8">
-        <v>159</v>
-      </c>
-      <c r="AF8">
-        <v>121</v>
-      </c>
-      <c r="AG8">
-        <v>60</v>
-      </c>
-      <c r="AH8">
-        <v>311</v>
-      </c>
-      <c r="AI8">
-        <v>70</v>
-      </c>
-      <c r="AJ8">
-        <v>136</v>
-      </c>
-      <c r="AK8">
-        <v>672</v>
-      </c>
-      <c r="AL8">
-        <v>60</v>
-      </c>
-      <c r="AM8">
-        <v>398</v>
-      </c>
-      <c r="AN8">
-        <v>1196</v>
-      </c>
-      <c r="AO8">
-        <v>66</v>
-      </c>
-      <c r="AP8">
-        <v>37</v>
-      </c>
-      <c r="AQ8">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="9" spans="1:43">
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E9,H9,K9,N9,Q9,T9)</f>
         <v>562</v>
       </c>
       <c r="C9">
@@ -1884,77 +1386,13 @@
       <c r="V9">
         <v>501</v>
       </c>
-      <c r="W9" s="2">
-        <f t="shared" si="1"/>
-        <v>562</v>
-      </c>
-      <c r="X9">
-        <v>9</v>
-      </c>
-      <c r="Y9">
-        <v>309</v>
-      </c>
-      <c r="Z9">
-        <v>105</v>
-      </c>
-      <c r="AA9">
-        <v>187</v>
-      </c>
-      <c r="AB9">
-        <v>717</v>
-      </c>
-      <c r="AC9">
-        <v>114</v>
-      </c>
-      <c r="AD9">
-        <v>62</v>
-      </c>
-      <c r="AE9">
-        <v>262</v>
-      </c>
-      <c r="AF9">
-        <v>135</v>
-      </c>
-      <c r="AG9">
-        <v>3</v>
-      </c>
-      <c r="AH9">
-        <v>20</v>
-      </c>
-      <c r="AI9">
-        <v>59</v>
-      </c>
-      <c r="AJ9">
-        <v>340</v>
-      </c>
-      <c r="AK9">
-        <v>1091</v>
-      </c>
-      <c r="AL9">
-        <v>85</v>
-      </c>
-      <c r="AM9">
-        <v>22</v>
-      </c>
-      <c r="AN9">
-        <v>215</v>
-      </c>
-      <c r="AO9">
-        <v>64</v>
-      </c>
-      <c r="AP9">
-        <v>54</v>
-      </c>
-      <c r="AQ9">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="10" spans="1:43">
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E10,H10,K10,N10,Q10,T10)</f>
         <v>544</v>
       </c>
       <c r="C10">
@@ -2017,77 +1455,13 @@
       <c r="V10">
         <v>825</v>
       </c>
-      <c r="W10" s="2">
-        <f t="shared" si="1"/>
-        <v>544</v>
-      </c>
-      <c r="X10">
-        <v>9</v>
-      </c>
-      <c r="Y10">
-        <v>309</v>
-      </c>
-      <c r="Z10">
-        <v>119</v>
-      </c>
-      <c r="AA10">
-        <v>3</v>
-      </c>
-      <c r="AB10">
-        <v>41</v>
-      </c>
-      <c r="AC10">
-        <v>114</v>
-      </c>
-      <c r="AD10">
-        <v>62</v>
-      </c>
-      <c r="AE10">
-        <v>262</v>
-      </c>
-      <c r="AF10">
-        <v>96</v>
-      </c>
-      <c r="AG10">
-        <v>438</v>
-      </c>
-      <c r="AH10">
-        <v>1273</v>
-      </c>
-      <c r="AI10">
-        <v>80</v>
-      </c>
-      <c r="AJ10">
-        <v>38</v>
-      </c>
-      <c r="AK10">
-        <v>317</v>
-      </c>
-      <c r="AL10">
-        <v>79</v>
-      </c>
-      <c r="AM10">
-        <v>60</v>
-      </c>
-      <c r="AN10">
-        <v>395</v>
-      </c>
-      <c r="AO10">
-        <v>56</v>
-      </c>
-      <c r="AP10">
-        <v>151</v>
-      </c>
-      <c r="AQ10">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="11" spans="1:43">
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" t="s">
         <v>35</v>
       </c>
       <c r="B11" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E11,H11,K11,N11,Q11,T11)</f>
         <v>537</v>
       </c>
       <c r="C11">
@@ -2150,77 +1524,13 @@
       <c r="V11">
         <v>912</v>
       </c>
-      <c r="W11" s="2">
-        <f t="shared" si="1"/>
-        <v>537</v>
-      </c>
-      <c r="X11">
-        <v>72</v>
-      </c>
-      <c r="Y11">
-        <v>669</v>
-      </c>
-      <c r="Z11">
-        <v>100</v>
-      </c>
-      <c r="AA11">
-        <v>367</v>
-      </c>
-      <c r="AB11">
-        <v>1104</v>
-      </c>
-      <c r="AC11">
-        <v>111</v>
-      </c>
-      <c r="AD11">
-        <v>89</v>
-      </c>
-      <c r="AE11">
-        <v>330</v>
-      </c>
-      <c r="AF11">
-        <v>126</v>
-      </c>
-      <c r="AG11">
-        <v>17</v>
-      </c>
-      <c r="AH11">
-        <v>147</v>
-      </c>
-      <c r="AI11">
-        <v>69</v>
-      </c>
-      <c r="AJ11">
-        <v>146</v>
-      </c>
-      <c r="AK11">
-        <v>695</v>
-      </c>
-      <c r="AL11">
-        <v>78</v>
-      </c>
-      <c r="AM11">
-        <v>84</v>
-      </c>
-      <c r="AN11">
-        <v>476</v>
-      </c>
-      <c r="AO11">
-        <v>53</v>
-      </c>
-      <c r="AP11">
-        <v>192</v>
-      </c>
-      <c r="AQ11">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="12" spans="1:43">
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E12,H12,K12,N12,Q12,T12)</f>
         <v>542</v>
       </c>
       <c r="C12">
@@ -2283,77 +1593,13 @@
       <c r="V12">
         <v>825</v>
       </c>
-      <c r="W12" s="2">
-        <f t="shared" si="1"/>
-        <v>542</v>
-      </c>
-      <c r="X12">
-        <v>72</v>
-      </c>
-      <c r="Y12">
-        <v>669</v>
-      </c>
-      <c r="Z12">
-        <v>99</v>
-      </c>
-      <c r="AA12">
-        <v>412</v>
-      </c>
-      <c r="AB12">
-        <v>1185</v>
-      </c>
-      <c r="AC12">
-        <v>117</v>
-      </c>
-      <c r="AD12">
-        <v>41</v>
-      </c>
-      <c r="AE12">
-        <v>197</v>
-      </c>
-      <c r="AF12">
-        <v>102</v>
-      </c>
-      <c r="AG12">
-        <v>318</v>
-      </c>
-      <c r="AH12">
-        <v>1059</v>
-      </c>
-      <c r="AI12">
-        <v>87</v>
-      </c>
-      <c r="AJ12">
-        <v>9</v>
-      </c>
-      <c r="AK12">
-        <v>120</v>
-      </c>
-      <c r="AL12">
-        <v>81</v>
-      </c>
-      <c r="AM12">
-        <v>38</v>
-      </c>
-      <c r="AN12">
-        <v>306</v>
-      </c>
-      <c r="AO12">
-        <v>56</v>
-      </c>
-      <c r="AP12">
-        <v>151</v>
-      </c>
-      <c r="AQ12">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="13" spans="1:43">
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" t="s">
         <v>92</v>
       </c>
       <c r="B13" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E13,H13,K13,N13,Q13,T13)</f>
         <v>535</v>
       </c>
       <c r="C13">
@@ -2416,77 +1662,13 @@
       <c r="V13">
         <v>825</v>
       </c>
-      <c r="W13" s="2">
-        <f t="shared" si="1"/>
-        <v>535</v>
-      </c>
-      <c r="X13">
-        <v>63</v>
-      </c>
-      <c r="Y13">
-        <v>637</v>
-      </c>
-      <c r="Z13">
-        <v>107</v>
-      </c>
-      <c r="AA13">
-        <v>117</v>
-      </c>
-      <c r="AB13">
-        <v>559</v>
-      </c>
-      <c r="AC13">
-        <v>99</v>
-      </c>
-      <c r="AD13">
-        <v>241</v>
-      </c>
-      <c r="AE13">
-        <v>710</v>
-      </c>
-      <c r="AF13">
-        <v>119</v>
-      </c>
-      <c r="AG13">
-        <v>80</v>
-      </c>
-      <c r="AH13">
-        <v>392</v>
-      </c>
-      <c r="AI13">
-        <v>79</v>
-      </c>
-      <c r="AJ13">
-        <v>42</v>
-      </c>
-      <c r="AK13">
-        <v>342</v>
-      </c>
-      <c r="AL13">
-        <v>76</v>
-      </c>
-      <c r="AM13">
-        <v>102</v>
-      </c>
-      <c r="AN13">
-        <v>541</v>
-      </c>
-      <c r="AO13">
-        <v>55</v>
-      </c>
-      <c r="AP13">
-        <v>151</v>
-      </c>
-      <c r="AQ13">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="14" spans="1:43">
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E14,H14,K14,N14,Q14,T14)</f>
         <v>562</v>
       </c>
       <c r="C14">
@@ -2549,77 +1731,13 @@
       <c r="V14">
         <v>501</v>
       </c>
-      <c r="W14" s="2">
-        <f t="shared" si="1"/>
-        <v>562</v>
-      </c>
-      <c r="X14">
-        <v>47</v>
-      </c>
-      <c r="Y14">
-        <v>541</v>
-      </c>
-      <c r="Z14">
-        <v>110</v>
-      </c>
-      <c r="AA14">
-        <v>54</v>
-      </c>
-      <c r="AB14">
-        <v>360</v>
-      </c>
-      <c r="AC14">
-        <v>108</v>
-      </c>
-      <c r="AD14">
-        <v>128</v>
-      </c>
-      <c r="AE14">
-        <v>418</v>
-      </c>
-      <c r="AF14">
-        <v>114</v>
-      </c>
-      <c r="AG14">
-        <v>126</v>
-      </c>
-      <c r="AH14">
-        <v>591</v>
-      </c>
-      <c r="AI14">
-        <v>71</v>
-      </c>
-      <c r="AJ14">
-        <v>122</v>
-      </c>
-      <c r="AK14">
-        <v>632</v>
-      </c>
-      <c r="AL14">
-        <v>94</v>
-      </c>
-      <c r="AM14">
-        <v>3</v>
-      </c>
-      <c r="AN14">
-        <v>23</v>
-      </c>
-      <c r="AO14">
-        <v>65</v>
-      </c>
-      <c r="AP14">
-        <v>54</v>
-      </c>
-      <c r="AQ14">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="15" spans="1:43">
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E15,H15,K15,N15,Q15,T15)</f>
         <v>548</v>
       </c>
       <c r="C15">
@@ -2682,77 +1800,13 @@
       <c r="V15">
         <v>358</v>
       </c>
-      <c r="W15" s="2">
-        <f t="shared" si="1"/>
-        <v>548</v>
-      </c>
-      <c r="X15">
-        <v>35</v>
-      </c>
-      <c r="Y15">
-        <v>479</v>
-      </c>
-      <c r="Z15">
-        <v>97</v>
-      </c>
-      <c r="AA15">
-        <v>490</v>
-      </c>
-      <c r="AB15">
-        <v>1318</v>
-      </c>
-      <c r="AC15">
-        <v>120</v>
-      </c>
-      <c r="AD15">
-        <v>27</v>
-      </c>
-      <c r="AE15">
-        <v>145</v>
-      </c>
-      <c r="AF15">
-        <v>101</v>
-      </c>
-      <c r="AG15">
-        <v>331</v>
-      </c>
-      <c r="AH15">
-        <v>1095</v>
-      </c>
-      <c r="AI15">
-        <v>84</v>
-      </c>
-      <c r="AJ15">
-        <v>14</v>
-      </c>
-      <c r="AK15">
-        <v>185</v>
-      </c>
-      <c r="AL15">
-        <v>78</v>
-      </c>
-      <c r="AM15">
-        <v>84</v>
-      </c>
-      <c r="AN15">
-        <v>476</v>
-      </c>
-      <c r="AO15">
-        <v>68</v>
-      </c>
-      <c r="AP15">
-        <v>26</v>
-      </c>
-      <c r="AQ15">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="16" spans="1:43">
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" t="s">
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E16,H16,K16,N16,Q16,T16)</f>
         <v>543</v>
       </c>
       <c r="C16">
@@ -2815,77 +1869,13 @@
       <c r="V16">
         <v>645</v>
       </c>
-      <c r="W16" s="2">
-        <f t="shared" si="1"/>
-        <v>543</v>
-      </c>
-      <c r="X16">
-        <v>87</v>
-      </c>
-      <c r="Y16">
-        <v>720</v>
-      </c>
-      <c r="Z16">
-        <v>95</v>
-      </c>
-      <c r="AA16">
-        <v>569</v>
-      </c>
-      <c r="AB16">
-        <v>1430</v>
-      </c>
-      <c r="AC16">
-        <v>121</v>
-      </c>
-      <c r="AD16">
-        <v>19</v>
-      </c>
-      <c r="AE16">
-        <v>124</v>
-      </c>
-      <c r="AF16">
-        <v>113</v>
-      </c>
-      <c r="AG16">
-        <v>142</v>
-      </c>
-      <c r="AH16">
-        <v>630</v>
-      </c>
-      <c r="AI16">
-        <v>72</v>
-      </c>
-      <c r="AJ16">
-        <v>105</v>
-      </c>
-      <c r="AK16">
-        <v>591</v>
-      </c>
-      <c r="AL16">
-        <v>82</v>
-      </c>
-      <c r="AM16">
-        <v>38</v>
-      </c>
-      <c r="AN16">
-        <v>306</v>
-      </c>
-      <c r="AO16">
-        <v>60</v>
-      </c>
-      <c r="AP16">
-        <v>94</v>
-      </c>
-      <c r="AQ16">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="17" spans="1:43">
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" t="s">
         <v>37</v>
       </c>
       <c r="B17" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E17,H17,K17,N17,Q17,T17)</f>
         <v>523</v>
       </c>
       <c r="C17">
@@ -2948,77 +1938,13 @@
       <c r="V17">
         <v>645</v>
       </c>
-      <c r="W17" s="2">
-        <f t="shared" si="1"/>
-        <v>523</v>
-      </c>
-      <c r="X17">
-        <v>47</v>
-      </c>
-      <c r="Y17">
-        <v>541</v>
-      </c>
-      <c r="Z17">
-        <v>115</v>
-      </c>
-      <c r="AA17">
-        <v>11</v>
-      </c>
-      <c r="AB17">
-        <v>123</v>
-      </c>
-      <c r="AC17">
-        <v>117</v>
-      </c>
-      <c r="AD17">
-        <v>41</v>
-      </c>
-      <c r="AE17">
-        <v>197</v>
-      </c>
-      <c r="AF17">
-        <v>111</v>
-      </c>
-      <c r="AG17">
-        <v>167</v>
-      </c>
-      <c r="AH17">
-        <v>707</v>
-      </c>
-      <c r="AI17">
-        <v>58</v>
-      </c>
-      <c r="AJ17">
-        <v>358</v>
-      </c>
-      <c r="AK17">
-        <v>1125</v>
-      </c>
-      <c r="AL17">
-        <v>62</v>
-      </c>
-      <c r="AM17">
-        <v>398</v>
-      </c>
-      <c r="AN17">
-        <v>1196</v>
-      </c>
-      <c r="AO17">
-        <v>60</v>
-      </c>
-      <c r="AP17">
-        <v>94</v>
-      </c>
-      <c r="AQ17">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="18" spans="1:43">
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E18,H18,K18,N18,Q18,T18)</f>
         <v>547</v>
       </c>
       <c r="C18">
@@ -3081,77 +2007,13 @@
       <c r="V18">
         <v>358</v>
       </c>
-      <c r="W18" s="2">
-        <f t="shared" si="1"/>
-        <v>547</v>
-      </c>
-      <c r="X18">
-        <v>11</v>
-      </c>
-      <c r="Y18">
-        <v>322</v>
-      </c>
-      <c r="Z18">
-        <v>109</v>
-      </c>
-      <c r="AA18">
-        <v>67</v>
-      </c>
-      <c r="AB18">
-        <v>415</v>
-      </c>
-      <c r="AC18">
-        <v>114</v>
-      </c>
-      <c r="AD18">
-        <v>62</v>
-      </c>
-      <c r="AE18">
-        <v>262</v>
-      </c>
-      <c r="AF18">
-        <v>106</v>
-      </c>
-      <c r="AG18">
-        <v>252</v>
-      </c>
-      <c r="AH18">
-        <v>907</v>
-      </c>
-      <c r="AI18">
-        <v>72</v>
-      </c>
-      <c r="AJ18">
-        <v>105</v>
-      </c>
-      <c r="AK18">
-        <v>591</v>
-      </c>
-      <c r="AL18">
-        <v>78</v>
-      </c>
-      <c r="AM18">
-        <v>84</v>
-      </c>
-      <c r="AN18">
-        <v>476</v>
-      </c>
-      <c r="AO18">
-        <v>68</v>
-      </c>
-      <c r="AP18">
-        <v>26</v>
-      </c>
-      <c r="AQ18">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="19" spans="1:43">
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E19,H19,K19,N19,Q19,T19)</f>
         <v>542</v>
       </c>
       <c r="C19">
@@ -3214,77 +2076,13 @@
       <c r="V19">
         <v>645</v>
       </c>
-      <c r="W19" s="2">
-        <f t="shared" si="1"/>
-        <v>542</v>
-      </c>
-      <c r="X19">
-        <v>63</v>
-      </c>
-      <c r="Y19">
-        <v>637</v>
-      </c>
-      <c r="Z19">
-        <v>109</v>
-      </c>
-      <c r="AA19">
-        <v>67</v>
-      </c>
-      <c r="AB19">
-        <v>415</v>
-      </c>
-      <c r="AC19">
-        <v>106</v>
-      </c>
-      <c r="AD19">
-        <v>152</v>
-      </c>
-      <c r="AE19">
-        <v>477</v>
-      </c>
-      <c r="AF19">
-        <v>111</v>
-      </c>
-      <c r="AG19">
-        <v>167</v>
-      </c>
-      <c r="AH19">
-        <v>707</v>
-      </c>
-      <c r="AI19">
-        <v>74</v>
-      </c>
-      <c r="AJ19">
-        <v>84</v>
-      </c>
-      <c r="AK19">
-        <v>513</v>
-      </c>
-      <c r="AL19">
-        <v>82</v>
-      </c>
-      <c r="AM19">
-        <v>38</v>
-      </c>
-      <c r="AN19">
-        <v>306</v>
-      </c>
-      <c r="AO19">
-        <v>60</v>
-      </c>
-      <c r="AP19">
-        <v>94</v>
-      </c>
-      <c r="AQ19">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="20" spans="1:43">
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E20,H20,K20,N20,Q20,T20)</f>
         <v>535</v>
       </c>
       <c r="C20">
@@ -3347,77 +2145,13 @@
       <c r="V20">
         <v>195</v>
       </c>
-      <c r="W20" s="2">
-        <f t="shared" si="1"/>
-        <v>535</v>
-      </c>
-      <c r="X20">
-        <v>52</v>
-      </c>
-      <c r="Y20">
-        <v>564</v>
-      </c>
-      <c r="Z20">
-        <v>109</v>
-      </c>
-      <c r="AA20">
-        <v>67</v>
-      </c>
-      <c r="AB20">
-        <v>415</v>
-      </c>
-      <c r="AC20">
-        <v>103</v>
-      </c>
-      <c r="AD20">
-        <v>182</v>
-      </c>
-      <c r="AE20">
-        <v>576</v>
-      </c>
-      <c r="AF20">
-        <v>123</v>
-      </c>
-      <c r="AG20">
-        <v>36</v>
-      </c>
-      <c r="AH20">
-        <v>233</v>
-      </c>
-      <c r="AI20">
-        <v>63</v>
-      </c>
-      <c r="AJ20">
-        <v>270</v>
-      </c>
-      <c r="AK20">
-        <v>944</v>
-      </c>
-      <c r="AL20">
-        <v>62</v>
-      </c>
-      <c r="AM20">
-        <v>398</v>
-      </c>
-      <c r="AN20">
-        <v>1196</v>
-      </c>
-      <c r="AO20">
-        <v>75</v>
-      </c>
-      <c r="AP20">
-        <v>9</v>
-      </c>
-      <c r="AQ20">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="21" spans="1:43">
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E21,H21,K21,N21,Q21,T21)</f>
         <v>568</v>
       </c>
       <c r="C21">
@@ -3480,77 +2214,13 @@
       <c r="V21">
         <v>195</v>
       </c>
-      <c r="W21" s="2">
-        <f t="shared" si="1"/>
-        <v>568</v>
-      </c>
-      <c r="X21">
-        <v>26</v>
-      </c>
-      <c r="Y21">
-        <v>438</v>
-      </c>
-      <c r="Z21">
-        <v>95</v>
-      </c>
-      <c r="AA21">
-        <v>569</v>
-      </c>
-      <c r="AB21">
-        <v>1430</v>
-      </c>
-      <c r="AC21">
-        <v>111</v>
-      </c>
-      <c r="AD21">
-        <v>89</v>
-      </c>
-      <c r="AE21">
-        <v>330</v>
-      </c>
-      <c r="AF21">
-        <v>112</v>
-      </c>
-      <c r="AG21">
-        <v>150</v>
-      </c>
-      <c r="AH21">
-        <v>664</v>
-      </c>
-      <c r="AI21">
-        <v>79</v>
-      </c>
-      <c r="AJ21">
-        <v>42</v>
-      </c>
-      <c r="AK21">
-        <v>342</v>
-      </c>
-      <c r="AL21">
-        <v>96</v>
-      </c>
-      <c r="AM21">
-        <v>1</v>
-      </c>
-      <c r="AN21">
-        <v>7</v>
-      </c>
-      <c r="AO21">
-        <v>75</v>
-      </c>
-      <c r="AP21">
-        <v>9</v>
-      </c>
-      <c r="AQ21">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="22" spans="1:43">
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E22,H22,K22,N22,Q22,T22)</f>
         <v>513</v>
       </c>
       <c r="C22">
@@ -3613,77 +2283,13 @@
       <c r="V22">
         <v>1034</v>
       </c>
-      <c r="W22" s="2">
-        <f t="shared" si="1"/>
-        <v>513</v>
-      </c>
-      <c r="X22">
-        <v>289</v>
-      </c>
-      <c r="Y22">
-        <v>1117</v>
-      </c>
-      <c r="Z22">
-        <v>102</v>
-      </c>
-      <c r="AA22">
-        <v>306</v>
-      </c>
-      <c r="AB22">
-        <v>979</v>
-      </c>
-      <c r="AC22">
-        <v>111</v>
-      </c>
-      <c r="AD22">
-        <v>89</v>
-      </c>
-      <c r="AE22">
-        <v>330</v>
-      </c>
-      <c r="AF22">
-        <v>114</v>
-      </c>
-      <c r="AG22">
-        <v>126</v>
-      </c>
-      <c r="AH22">
-        <v>591</v>
-      </c>
-      <c r="AI22">
-        <v>70</v>
-      </c>
-      <c r="AJ22">
-        <v>136</v>
-      </c>
-      <c r="AK22">
-        <v>672</v>
-      </c>
-      <c r="AL22">
-        <v>65</v>
-      </c>
-      <c r="AM22">
-        <v>279</v>
-      </c>
-      <c r="AN22">
-        <v>1002</v>
-      </c>
-      <c r="AO22">
-        <v>51</v>
-      </c>
-      <c r="AP22">
-        <v>263</v>
-      </c>
-      <c r="AQ22">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="23" spans="1:43">
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E23,H23,K23,N23,Q23,T23)</f>
         <v>527</v>
       </c>
       <c r="C23">
@@ -3746,77 +2352,13 @@
       <c r="V23">
         <v>645</v>
       </c>
-      <c r="W23" s="2">
-        <f t="shared" si="1"/>
-        <v>527</v>
-      </c>
-      <c r="X23">
-        <v>124</v>
-      </c>
-      <c r="Y23">
-        <v>813</v>
-      </c>
-      <c r="Z23">
-        <v>105</v>
-      </c>
-      <c r="AA23">
-        <v>187</v>
-      </c>
-      <c r="AB23">
-        <v>717</v>
-      </c>
-      <c r="AC23">
-        <v>121</v>
-      </c>
-      <c r="AD23">
-        <v>19</v>
-      </c>
-      <c r="AE23">
-        <v>124</v>
-      </c>
-      <c r="AF23">
-        <v>99</v>
-      </c>
-      <c r="AG23">
-        <v>371</v>
-      </c>
-      <c r="AH23">
-        <v>1171</v>
-      </c>
-      <c r="AI23">
-        <v>71</v>
-      </c>
-      <c r="AJ23">
-        <v>122</v>
-      </c>
-      <c r="AK23">
-        <v>632</v>
-      </c>
-      <c r="AL23">
-        <v>70</v>
-      </c>
-      <c r="AM23">
-        <v>206</v>
-      </c>
-      <c r="AN23">
-        <v>852</v>
-      </c>
-      <c r="AO23">
-        <v>61</v>
-      </c>
-      <c r="AP23">
-        <v>94</v>
-      </c>
-      <c r="AQ23">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="24" spans="1:43">
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" t="s">
         <v>33</v>
       </c>
       <c r="B24" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E24,H24,K24,N24,Q24,T24)</f>
         <v>535</v>
       </c>
       <c r="C24">
@@ -3879,77 +2421,13 @@
       <c r="V24">
         <v>578</v>
       </c>
-      <c r="W24" s="2">
-        <f t="shared" si="1"/>
-        <v>535</v>
-      </c>
-      <c r="X24">
-        <v>163</v>
-      </c>
-      <c r="Y24">
-        <v>889</v>
-      </c>
-      <c r="Z24">
-        <v>102</v>
-      </c>
-      <c r="AA24">
-        <v>306</v>
-      </c>
-      <c r="AB24">
-        <v>979</v>
-      </c>
-      <c r="AC24">
-        <v>123</v>
-      </c>
-      <c r="AD24">
-        <v>15</v>
-      </c>
-      <c r="AE24">
-        <v>101</v>
-      </c>
-      <c r="AF24">
-        <v>100</v>
-      </c>
-      <c r="AG24">
-        <v>353</v>
-      </c>
-      <c r="AH24">
-        <v>1137</v>
-      </c>
-      <c r="AI24">
-        <v>68</v>
-      </c>
-      <c r="AJ24">
-        <v>169</v>
-      </c>
-      <c r="AK24">
-        <v>740</v>
-      </c>
-      <c r="AL24">
-        <v>80</v>
-      </c>
-      <c r="AM24">
-        <v>60</v>
-      </c>
-      <c r="AN24">
-        <v>395</v>
-      </c>
-      <c r="AO24">
-        <v>62</v>
-      </c>
-      <c r="AP24">
-        <v>73</v>
-      </c>
-      <c r="AQ24">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="25" spans="1:43">
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E25,H25,K25,N25,Q25,T25)</f>
         <v>514</v>
       </c>
       <c r="C25">
@@ -4012,77 +2490,13 @@
       <c r="V25">
         <v>912</v>
       </c>
-      <c r="W25" s="2">
-        <f t="shared" si="1"/>
-        <v>514</v>
-      </c>
-      <c r="X25">
-        <v>98</v>
-      </c>
-      <c r="Y25">
-        <v>744</v>
-      </c>
-      <c r="Z25">
-        <v>101</v>
-      </c>
-      <c r="AA25">
-        <v>335</v>
-      </c>
-      <c r="AB25">
-        <v>1041</v>
-      </c>
-      <c r="AC25">
-        <v>111</v>
-      </c>
-      <c r="AD25">
-        <v>89</v>
-      </c>
-      <c r="AE25">
-        <v>330</v>
-      </c>
-      <c r="AF25">
-        <v>116</v>
-      </c>
-      <c r="AG25">
-        <v>109</v>
-      </c>
-      <c r="AH25">
-        <v>514</v>
-      </c>
-      <c r="AI25">
-        <v>64</v>
-      </c>
-      <c r="AJ25">
-        <v>245</v>
-      </c>
-      <c r="AK25">
-        <v>901</v>
-      </c>
-      <c r="AL25">
-        <v>70</v>
-      </c>
-      <c r="AM25">
-        <v>206</v>
-      </c>
-      <c r="AN25">
-        <v>852</v>
-      </c>
-      <c r="AO25">
-        <v>52</v>
-      </c>
-      <c r="AP25">
-        <v>192</v>
-      </c>
-      <c r="AQ25">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="26" spans="1:43">
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" t="s">
         <v>39</v>
       </c>
       <c r="B26" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E26,H26,K26,N26,Q26,T26)</f>
         <v>538</v>
       </c>
       <c r="C26">
@@ -4145,77 +2559,13 @@
       <c r="V26">
         <v>424</v>
       </c>
-      <c r="W26" s="2">
-        <f t="shared" si="1"/>
-        <v>538</v>
-      </c>
-      <c r="X26">
-        <v>37</v>
-      </c>
-      <c r="Y26">
-        <v>494</v>
-      </c>
-      <c r="Z26">
-        <v>104</v>
-      </c>
-      <c r="AA26">
-        <v>224</v>
-      </c>
-      <c r="AB26">
-        <v>808</v>
-      </c>
-      <c r="AC26">
-        <v>95</v>
-      </c>
-      <c r="AD26">
-        <v>296</v>
-      </c>
-      <c r="AE26">
-        <v>848</v>
-      </c>
-      <c r="AF26">
-        <v>128</v>
-      </c>
-      <c r="AG26">
-        <v>11</v>
-      </c>
-      <c r="AH26">
-        <v>108</v>
-      </c>
-      <c r="AI26">
-        <v>63</v>
-      </c>
-      <c r="AJ26">
-        <v>270</v>
-      </c>
-      <c r="AK26">
-        <v>944</v>
-      </c>
-      <c r="AL26">
-        <v>82</v>
-      </c>
-      <c r="AM26">
-        <v>38</v>
-      </c>
-      <c r="AN26">
-        <v>306</v>
-      </c>
-      <c r="AO26">
-        <v>66</v>
-      </c>
-      <c r="AP26">
-        <v>37</v>
-      </c>
-      <c r="AQ26">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="27" spans="1:43">
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" t="s">
         <v>14</v>
       </c>
       <c r="B27" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E27,H27,K27,N27,Q27,T27)</f>
         <v>515</v>
       </c>
       <c r="C27">
@@ -4278,77 +2628,13 @@
       <c r="V27">
         <v>721</v>
       </c>
-      <c r="W27" s="2">
-        <f t="shared" si="1"/>
-        <v>515</v>
-      </c>
-      <c r="X27">
-        <v>159</v>
-      </c>
-      <c r="Y27">
-        <v>878</v>
-      </c>
-      <c r="Z27">
-        <v>94</v>
-      </c>
-      <c r="AA27">
-        <v>604</v>
-      </c>
-      <c r="AB27">
-        <v>1485</v>
-      </c>
-      <c r="AC27">
-        <v>115</v>
-      </c>
-      <c r="AD27">
-        <v>58</v>
-      </c>
-      <c r="AE27">
-        <v>236</v>
-      </c>
-      <c r="AF27">
-        <v>112</v>
-      </c>
-      <c r="AG27">
-        <v>150</v>
-      </c>
-      <c r="AH27">
-        <v>664</v>
-      </c>
-      <c r="AI27">
-        <v>68</v>
-      </c>
-      <c r="AJ27">
-        <v>169</v>
-      </c>
-      <c r="AK27">
-        <v>740</v>
-      </c>
-      <c r="AL27">
-        <v>69</v>
-      </c>
-      <c r="AM27">
-        <v>206</v>
-      </c>
-      <c r="AN27">
-        <v>852</v>
-      </c>
-      <c r="AO27">
-        <v>57</v>
-      </c>
-      <c r="AP27">
-        <v>115</v>
-      </c>
-      <c r="AQ27">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="28" spans="1:43">
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" t="s">
         <v>40</v>
       </c>
       <c r="B28" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E28,H28,K28,N28,Q28,T28)</f>
         <v>528</v>
       </c>
       <c r="C28">
@@ -4411,77 +2697,13 @@
       <c r="V28">
         <v>424</v>
       </c>
-      <c r="W28" s="2">
-        <f t="shared" si="1"/>
-        <v>528</v>
-      </c>
-      <c r="X28">
-        <v>40</v>
-      </c>
-      <c r="Y28">
-        <v>505</v>
-      </c>
-      <c r="Z28">
-        <v>95</v>
-      </c>
-      <c r="AA28">
-        <v>569</v>
-      </c>
-      <c r="AB28">
-        <v>1430</v>
-      </c>
-      <c r="AC28">
-        <v>92</v>
-      </c>
-      <c r="AD28">
-        <v>343</v>
-      </c>
-      <c r="AE28">
-        <v>950</v>
-      </c>
-      <c r="AF28">
-        <v>119</v>
-      </c>
-      <c r="AG28">
-        <v>80</v>
-      </c>
-      <c r="AH28">
-        <v>392</v>
-      </c>
-      <c r="AI28">
-        <v>82</v>
-      </c>
-      <c r="AJ28">
-        <v>22</v>
-      </c>
-      <c r="AK28">
-        <v>248</v>
-      </c>
-      <c r="AL28">
-        <v>74</v>
-      </c>
-      <c r="AM28">
-        <v>141</v>
-      </c>
-      <c r="AN28">
-        <v>675</v>
-      </c>
-      <c r="AO28">
-        <v>66</v>
-      </c>
-      <c r="AP28">
-        <v>37</v>
-      </c>
-      <c r="AQ28">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="29" spans="1:43">
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E29,H29,K29,N29,Q29,T29)</f>
         <v>508</v>
       </c>
       <c r="C29">
@@ -4544,77 +2766,13 @@
       <c r="V29">
         <v>1320</v>
       </c>
-      <c r="W29" s="2">
-        <f t="shared" si="1"/>
-        <v>508</v>
-      </c>
-      <c r="X29">
-        <v>124</v>
-      </c>
-      <c r="Y29">
-        <v>813</v>
-      </c>
-      <c r="Z29">
-        <v>103</v>
-      </c>
-      <c r="AA29">
-        <v>258</v>
-      </c>
-      <c r="AB29">
-        <v>882</v>
-      </c>
-      <c r="AC29">
-        <v>103</v>
-      </c>
-      <c r="AD29">
-        <v>182</v>
-      </c>
-      <c r="AE29">
-        <v>576</v>
-      </c>
-      <c r="AF29">
-        <v>120</v>
-      </c>
-      <c r="AG29">
-        <v>73</v>
-      </c>
-      <c r="AH29">
-        <v>350</v>
-      </c>
-      <c r="AI29">
-        <v>61</v>
-      </c>
-      <c r="AJ29">
-        <v>303</v>
-      </c>
-      <c r="AK29">
-        <v>1011</v>
-      </c>
-      <c r="AL29">
-        <v>78</v>
-      </c>
-      <c r="AM29">
-        <v>84</v>
-      </c>
-      <c r="AN29">
-        <v>476</v>
-      </c>
-      <c r="AO29">
-        <v>43</v>
-      </c>
-      <c r="AP29">
-        <v>448</v>
-      </c>
-      <c r="AQ29">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="30" spans="1:43">
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E30,H30,K30,N30,Q30,T30)</f>
         <v>519</v>
       </c>
       <c r="C30">
@@ -4677,77 +2835,13 @@
       <c r="V30">
         <v>578</v>
       </c>
-      <c r="W30" s="2">
-        <f t="shared" si="1"/>
-        <v>519</v>
-      </c>
-      <c r="X30">
-        <v>167</v>
-      </c>
-      <c r="Y30">
-        <v>897</v>
-      </c>
-      <c r="Z30">
-        <v>99</v>
-      </c>
-      <c r="AA30">
-        <v>412</v>
-      </c>
-      <c r="AB30">
-        <v>1185</v>
-      </c>
-      <c r="AC30">
-        <v>104</v>
-      </c>
-      <c r="AD30">
-        <v>172</v>
-      </c>
-      <c r="AE30">
-        <v>540</v>
-      </c>
-      <c r="AF30">
-        <v>109</v>
-      </c>
-      <c r="AG30">
-        <v>193</v>
-      </c>
-      <c r="AH30">
-        <v>780</v>
-      </c>
-      <c r="AI30">
-        <v>74</v>
-      </c>
-      <c r="AJ30">
-        <v>84</v>
-      </c>
-      <c r="AK30">
-        <v>513</v>
-      </c>
-      <c r="AL30">
-        <v>70</v>
-      </c>
-      <c r="AM30">
-        <v>206</v>
-      </c>
-      <c r="AN30">
-        <v>852</v>
-      </c>
-      <c r="AO30">
-        <v>63</v>
-      </c>
-      <c r="AP30">
-        <v>73</v>
-      </c>
-      <c r="AQ30">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="31" spans="1:43">
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" t="s">
         <v>19</v>
       </c>
       <c r="B31" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E31,H31,K31,N31,Q31,T31)</f>
         <v>532</v>
       </c>
       <c r="C31">
@@ -4810,77 +2904,13 @@
       <c r="V31">
         <v>424</v>
       </c>
-      <c r="W31" s="2">
-        <f t="shared" si="1"/>
-        <v>532</v>
-      </c>
-      <c r="X31">
-        <v>98</v>
-      </c>
-      <c r="Y31">
-        <v>744</v>
-      </c>
-      <c r="Z31">
-        <v>107</v>
-      </c>
-      <c r="AA31">
-        <v>117</v>
-      </c>
-      <c r="AB31">
-        <v>559</v>
-      </c>
-      <c r="AC31">
-        <v>121</v>
-      </c>
-      <c r="AD31">
-        <v>19</v>
-      </c>
-      <c r="AE31">
-        <v>124</v>
-      </c>
-      <c r="AF31">
-        <v>96</v>
-      </c>
-      <c r="AG31">
-        <v>438</v>
-      </c>
-      <c r="AH31">
-        <v>1273</v>
-      </c>
-      <c r="AI31">
-        <v>62</v>
-      </c>
-      <c r="AJ31">
-        <v>285</v>
-      </c>
-      <c r="AK31">
-        <v>971</v>
-      </c>
-      <c r="AL31">
-        <v>79</v>
-      </c>
-      <c r="AM31">
-        <v>60</v>
-      </c>
-      <c r="AN31">
-        <v>395</v>
-      </c>
-      <c r="AO31">
-        <v>67</v>
-      </c>
-      <c r="AP31">
-        <v>37</v>
-      </c>
-      <c r="AQ31">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="32" spans="1:43">
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" t="s">
         <v>13</v>
       </c>
       <c r="B32" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E32,H32,K32,N32,Q32,T32)</f>
         <v>522</v>
       </c>
       <c r="C32">
@@ -4943,77 +2973,13 @@
       <c r="V32">
         <v>825</v>
       </c>
-      <c r="W32" s="2">
-        <f t="shared" si="1"/>
-        <v>522</v>
-      </c>
-      <c r="X32">
-        <v>167</v>
-      </c>
-      <c r="Y32">
-        <v>897</v>
-      </c>
-      <c r="Z32">
-        <v>84</v>
-      </c>
-      <c r="AA32">
-        <v>803</v>
-      </c>
-      <c r="AB32">
-        <v>1753</v>
-      </c>
-      <c r="AC32">
-        <v>111</v>
-      </c>
-      <c r="AD32">
-        <v>89</v>
-      </c>
-      <c r="AE32">
-        <v>330</v>
-      </c>
-      <c r="AF32">
-        <v>108</v>
-      </c>
-      <c r="AG32">
-        <v>206</v>
-      </c>
-      <c r="AH32">
-        <v>814</v>
-      </c>
-      <c r="AI32">
-        <v>83</v>
-      </c>
-      <c r="AJ32">
-        <v>19</v>
-      </c>
-      <c r="AK32">
-        <v>214</v>
-      </c>
-      <c r="AL32">
-        <v>80</v>
-      </c>
-      <c r="AM32">
-        <v>60</v>
-      </c>
-      <c r="AN32">
-        <v>395</v>
-      </c>
-      <c r="AO32">
-        <v>56</v>
-      </c>
-      <c r="AP32">
-        <v>151</v>
-      </c>
-      <c r="AQ32">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="33" spans="1:43">
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" t="s">
         <v>45</v>
       </c>
       <c r="B33" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E33,H33,K33,N33,Q33,T33)</f>
         <v>518</v>
       </c>
       <c r="C33">
@@ -5076,77 +3042,13 @@
       <c r="V33">
         <v>912</v>
       </c>
-      <c r="W33" s="2">
-        <f t="shared" si="1"/>
-        <v>518</v>
-      </c>
-      <c r="X33">
-        <v>62</v>
-      </c>
-      <c r="Y33">
-        <v>629</v>
-      </c>
-      <c r="Z33">
-        <v>108</v>
-      </c>
-      <c r="AA33">
-        <v>91</v>
-      </c>
-      <c r="AB33">
-        <v>485</v>
-      </c>
-      <c r="AC33">
-        <v>105</v>
-      </c>
-      <c r="AD33">
-        <v>160</v>
-      </c>
-      <c r="AE33">
-        <v>507</v>
-      </c>
-      <c r="AF33">
-        <v>106</v>
-      </c>
-      <c r="AG33">
-        <v>252</v>
-      </c>
-      <c r="AH33">
-        <v>907</v>
-      </c>
-      <c r="AI33">
-        <v>66</v>
-      </c>
-      <c r="AJ33">
-        <v>206</v>
-      </c>
-      <c r="AK33">
-        <v>828</v>
-      </c>
-      <c r="AL33">
-        <v>81</v>
-      </c>
-      <c r="AM33">
-        <v>38</v>
-      </c>
-      <c r="AN33">
-        <v>306</v>
-      </c>
-      <c r="AO33">
-        <v>52</v>
-      </c>
-      <c r="AP33">
-        <v>192</v>
-      </c>
-      <c r="AQ33">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="34" spans="1:43">
+    </row>
+    <row r="34" spans="1:22">
       <c r="A34" t="s">
         <v>16</v>
       </c>
       <c r="B34" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E34,H34,K34,N34,Q34,T34)</f>
         <v>506</v>
       </c>
       <c r="C34">
@@ -5209,77 +3111,13 @@
       <c r="V34">
         <v>645</v>
       </c>
-      <c r="W34" s="2">
-        <f t="shared" si="1"/>
-        <v>506</v>
-      </c>
-      <c r="X34">
-        <v>44</v>
-      </c>
-      <c r="Y34">
-        <v>524</v>
-      </c>
-      <c r="Z34">
-        <v>110</v>
-      </c>
-      <c r="AA34">
-        <v>54</v>
-      </c>
-      <c r="AB34">
-        <v>360</v>
-      </c>
-      <c r="AC34">
-        <v>91</v>
-      </c>
-      <c r="AD34">
-        <v>365</v>
-      </c>
-      <c r="AE34">
-        <v>990</v>
-      </c>
-      <c r="AF34">
-        <v>121</v>
-      </c>
-      <c r="AG34">
-        <v>60</v>
-      </c>
-      <c r="AH34">
-        <v>311</v>
-      </c>
-      <c r="AI34">
-        <v>63</v>
-      </c>
-      <c r="AJ34">
-        <v>270</v>
-      </c>
-      <c r="AK34">
-        <v>944</v>
-      </c>
-      <c r="AL34">
-        <v>60</v>
-      </c>
-      <c r="AM34">
-        <v>398</v>
-      </c>
-      <c r="AN34">
-        <v>1196</v>
-      </c>
-      <c r="AO34">
-        <v>61</v>
-      </c>
-      <c r="AP34">
-        <v>94</v>
-      </c>
-      <c r="AQ34">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="35" spans="1:43">
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35" t="s">
         <v>29</v>
       </c>
       <c r="B35" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E35,H35,K35,N35,Q35,T35)</f>
         <v>497</v>
       </c>
       <c r="C35">
@@ -5342,77 +3180,13 @@
       <c r="V35">
         <v>1034</v>
       </c>
-      <c r="W35" s="2">
-        <f t="shared" si="1"/>
-        <v>497</v>
-      </c>
-      <c r="X35">
-        <v>163</v>
-      </c>
-      <c r="Y35">
-        <v>889</v>
-      </c>
-      <c r="Z35">
-        <v>105</v>
-      </c>
-      <c r="AA35">
-        <v>187</v>
-      </c>
-      <c r="AB35">
-        <v>717</v>
-      </c>
-      <c r="AC35">
-        <v>107</v>
-      </c>
-      <c r="AD35">
-        <v>140</v>
-      </c>
-      <c r="AE35">
-        <v>451</v>
-      </c>
-      <c r="AF35">
-        <v>106</v>
-      </c>
-      <c r="AG35">
-        <v>252</v>
-      </c>
-      <c r="AH35">
-        <v>907</v>
-      </c>
-      <c r="AI35">
-        <v>66</v>
-      </c>
-      <c r="AJ35">
-        <v>206</v>
-      </c>
-      <c r="AK35">
-        <v>828</v>
-      </c>
-      <c r="AL35">
-        <v>64</v>
-      </c>
-      <c r="AM35">
-        <v>349</v>
-      </c>
-      <c r="AN35">
-        <v>1115</v>
-      </c>
-      <c r="AO35">
-        <v>49</v>
-      </c>
-      <c r="AP35">
-        <v>263</v>
-      </c>
-      <c r="AQ35">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="36" spans="1:43">
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36" t="s">
         <v>5</v>
       </c>
       <c r="B36" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E36,H36,K36,N36,Q36,T36)</f>
         <v>505</v>
       </c>
       <c r="C36">
@@ -5475,77 +3249,13 @@
       <c r="V36">
         <v>912</v>
       </c>
-      <c r="W36" s="2">
-        <f t="shared" si="1"/>
-        <v>505</v>
-      </c>
-      <c r="X36">
-        <v>145</v>
-      </c>
-      <c r="Y36">
-        <v>847</v>
-      </c>
-      <c r="Z36">
-        <v>102</v>
-      </c>
-      <c r="AA36">
-        <v>306</v>
-      </c>
-      <c r="AB36">
-        <v>979</v>
-      </c>
-      <c r="AC36">
-        <v>114</v>
-      </c>
-      <c r="AD36">
-        <v>62</v>
-      </c>
-      <c r="AE36">
-        <v>262</v>
-      </c>
-      <c r="AF36">
-        <v>117</v>
-      </c>
-      <c r="AG36">
-        <v>95</v>
-      </c>
-      <c r="AH36">
-        <v>471</v>
-      </c>
-      <c r="AI36">
-        <v>51</v>
-      </c>
-      <c r="AJ36">
-        <v>508</v>
-      </c>
-      <c r="AK36">
-        <v>1354</v>
-      </c>
-      <c r="AL36">
-        <v>67</v>
-      </c>
-      <c r="AM36">
-        <v>279</v>
-      </c>
-      <c r="AN36">
-        <v>1002</v>
-      </c>
-      <c r="AO36">
-        <v>54</v>
-      </c>
-      <c r="AP36">
-        <v>192</v>
-      </c>
-      <c r="AQ36">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="37" spans="1:43">
+    </row>
+    <row r="37" spans="1:22">
       <c r="A37" t="s">
         <v>3</v>
       </c>
       <c r="B37" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E37,H37,K37,N37,Q37,T37)</f>
         <v>514</v>
       </c>
       <c r="C37">
@@ -5608,77 +3318,13 @@
       <c r="V37">
         <v>578</v>
       </c>
-      <c r="W37" s="2">
-        <f t="shared" si="1"/>
-        <v>514</v>
-      </c>
-      <c r="X37">
-        <v>124</v>
-      </c>
-      <c r="Y37">
-        <v>813</v>
-      </c>
-      <c r="Z37">
-        <v>95</v>
-      </c>
-      <c r="AA37">
-        <v>569</v>
-      </c>
-      <c r="AB37">
-        <v>1430</v>
-      </c>
-      <c r="AC37">
-        <v>114</v>
-      </c>
-      <c r="AD37">
-        <v>62</v>
-      </c>
-      <c r="AE37">
-        <v>262</v>
-      </c>
-      <c r="AF37">
-        <v>110</v>
-      </c>
-      <c r="AG37">
-        <v>181</v>
-      </c>
-      <c r="AH37">
-        <v>740</v>
-      </c>
-      <c r="AI37">
-        <v>65</v>
-      </c>
-      <c r="AJ37">
-        <v>226</v>
-      </c>
-      <c r="AK37">
-        <v>867</v>
-      </c>
-      <c r="AL37">
-        <v>68</v>
-      </c>
-      <c r="AM37">
-        <v>206</v>
-      </c>
-      <c r="AN37">
-        <v>852</v>
-      </c>
-      <c r="AO37">
-        <v>62</v>
-      </c>
-      <c r="AP37">
-        <v>73</v>
-      </c>
-      <c r="AQ37">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="38" spans="1:43">
+    </row>
+    <row r="38" spans="1:22">
       <c r="A38" t="s">
         <v>20</v>
       </c>
       <c r="B38" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E38,H38,K38,N38,Q38,T38)</f>
         <v>497</v>
       </c>
       <c r="C38">
@@ -5741,77 +3387,13 @@
       <c r="V38">
         <v>1034</v>
       </c>
-      <c r="W38" s="2">
-        <f t="shared" si="1"/>
-        <v>497</v>
-      </c>
-      <c r="X38">
-        <v>148</v>
-      </c>
-      <c r="Y38">
-        <v>855</v>
-      </c>
-      <c r="Z38">
-        <v>113</v>
-      </c>
-      <c r="AA38">
-        <v>25</v>
-      </c>
-      <c r="AB38">
-        <v>193</v>
-      </c>
-      <c r="AC38">
-        <v>103</v>
-      </c>
-      <c r="AD38">
-        <v>182</v>
-      </c>
-      <c r="AE38">
-        <v>576</v>
-      </c>
-      <c r="AF38">
-        <v>115</v>
-      </c>
-      <c r="AG38">
-        <v>114</v>
-      </c>
-      <c r="AH38">
-        <v>544</v>
-      </c>
-      <c r="AI38">
-        <v>51</v>
-      </c>
-      <c r="AJ38">
-        <v>508</v>
-      </c>
-      <c r="AK38">
-        <v>1354</v>
-      </c>
-      <c r="AL38">
-        <v>64</v>
-      </c>
-      <c r="AM38">
-        <v>349</v>
-      </c>
-      <c r="AN38">
-        <v>1115</v>
-      </c>
-      <c r="AO38">
-        <v>51</v>
-      </c>
-      <c r="AP38">
-        <v>263</v>
-      </c>
-      <c r="AQ38">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="39" spans="1:43">
+    </row>
+    <row r="39" spans="1:22">
       <c r="A39" t="s">
         <v>2</v>
       </c>
       <c r="B39" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E39,H39,K39,N39,Q39,T39)</f>
         <v>543</v>
       </c>
       <c r="C39">
@@ -5874,77 +3456,13 @@
       <c r="V39">
         <v>46</v>
       </c>
-      <c r="W39" s="2">
-        <f t="shared" si="1"/>
-        <v>543</v>
-      </c>
-      <c r="X39">
-        <v>68</v>
-      </c>
-      <c r="Y39">
-        <v>646</v>
-      </c>
-      <c r="Z39">
-        <v>109</v>
-      </c>
-      <c r="AA39">
-        <v>67</v>
-      </c>
-      <c r="AB39">
-        <v>415</v>
-      </c>
-      <c r="AC39">
-        <v>95</v>
-      </c>
-      <c r="AD39">
-        <v>296</v>
-      </c>
-      <c r="AE39">
-        <v>848</v>
-      </c>
-      <c r="AF39">
-        <v>109</v>
-      </c>
-      <c r="AG39">
-        <v>193</v>
-      </c>
-      <c r="AH39">
-        <v>780</v>
-      </c>
-      <c r="AI39">
-        <v>69</v>
-      </c>
-      <c r="AJ39">
-        <v>146</v>
-      </c>
-      <c r="AK39">
-        <v>695</v>
-      </c>
-      <c r="AL39">
-        <v>78</v>
-      </c>
-      <c r="AM39">
-        <v>84</v>
-      </c>
-      <c r="AN39">
-        <v>476</v>
-      </c>
-      <c r="AO39">
-        <v>83</v>
-      </c>
-      <c r="AP39">
-        <v>3</v>
-      </c>
-      <c r="AQ39">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:43">
+    </row>
+    <row r="40" spans="1:22">
       <c r="A40" t="s">
         <v>26</v>
       </c>
       <c r="B40" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E40,H40,K40,N40,Q40,T40)</f>
         <v>519</v>
       </c>
       <c r="C40">
@@ -6007,77 +3525,13 @@
       <c r="V40">
         <v>578</v>
       </c>
-      <c r="W40" s="2">
-        <f t="shared" si="1"/>
-        <v>519</v>
-      </c>
-      <c r="X40">
-        <v>140</v>
-      </c>
-      <c r="Y40">
-        <v>840</v>
-      </c>
-      <c r="Z40">
-        <v>108</v>
-      </c>
-      <c r="AA40">
-        <v>91</v>
-      </c>
-      <c r="AB40">
-        <v>485</v>
-      </c>
-      <c r="AC40">
-        <v>92</v>
-      </c>
-      <c r="AD40">
-        <v>343</v>
-      </c>
-      <c r="AE40">
-        <v>950</v>
-      </c>
-      <c r="AF40">
-        <v>112</v>
-      </c>
-      <c r="AG40">
-        <v>150</v>
-      </c>
-      <c r="AH40">
-        <v>664</v>
-      </c>
-      <c r="AI40">
-        <v>69</v>
-      </c>
-      <c r="AJ40">
-        <v>146</v>
-      </c>
-      <c r="AK40">
-        <v>695</v>
-      </c>
-      <c r="AL40">
-        <v>76</v>
-      </c>
-      <c r="AM40">
-        <v>102</v>
-      </c>
-      <c r="AN40">
-        <v>541</v>
-      </c>
-      <c r="AO40">
-        <v>62</v>
-      </c>
-      <c r="AP40">
-        <v>73</v>
-      </c>
-      <c r="AQ40">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="41" spans="1:43">
+    </row>
+    <row r="41" spans="1:22">
       <c r="A41" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E41,H41,K41,N41,Q41,T41)</f>
         <v>529</v>
       </c>
       <c r="C41">
@@ -6140,77 +3594,13 @@
       <c r="V41">
         <v>645</v>
       </c>
-      <c r="W41" s="2">
-        <f t="shared" si="1"/>
-        <v>529</v>
-      </c>
-      <c r="X41">
-        <v>81</v>
-      </c>
-      <c r="Y41">
-        <v>707</v>
-      </c>
-      <c r="Z41">
-        <v>109</v>
-      </c>
-      <c r="AA41">
-        <v>67</v>
-      </c>
-      <c r="AB41">
-        <v>415</v>
-      </c>
-      <c r="AC41">
-        <v>101</v>
-      </c>
-      <c r="AD41">
-        <v>215</v>
-      </c>
-      <c r="AE41">
-        <v>646</v>
-      </c>
-      <c r="AF41">
-        <v>95</v>
-      </c>
-      <c r="AG41">
-        <v>456</v>
-      </c>
-      <c r="AH41">
-        <v>1300</v>
-      </c>
-      <c r="AI41">
-        <v>72</v>
-      </c>
-      <c r="AJ41">
-        <v>105</v>
-      </c>
-      <c r="AK41">
-        <v>591</v>
-      </c>
-      <c r="AL41">
-        <v>92</v>
-      </c>
-      <c r="AM41">
-        <v>5</v>
-      </c>
-      <c r="AN41">
-        <v>43</v>
-      </c>
-      <c r="AO41">
-        <v>60</v>
-      </c>
-      <c r="AP41">
-        <v>94</v>
-      </c>
-      <c r="AQ41">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="42" spans="1:43">
+    </row>
+    <row r="42" spans="1:22">
       <c r="A42" t="s">
         <v>10</v>
       </c>
       <c r="B42" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E42,H42,K42,N42,Q42,T42)</f>
         <v>514</v>
       </c>
       <c r="C42">
@@ -6273,77 +3663,13 @@
       <c r="V42">
         <v>721</v>
       </c>
-      <c r="W42" s="2">
-        <f t="shared" si="1"/>
-        <v>514</v>
-      </c>
-      <c r="X42">
-        <v>419</v>
-      </c>
-      <c r="Y42">
-        <v>1289</v>
-      </c>
-      <c r="Z42">
-        <v>104</v>
-      </c>
-      <c r="AA42">
-        <v>224</v>
-      </c>
-      <c r="AB42">
-        <v>808</v>
-      </c>
-      <c r="AC42">
-        <v>102</v>
-      </c>
-      <c r="AD42">
-        <v>202</v>
-      </c>
-      <c r="AE42">
-        <v>612</v>
-      </c>
-      <c r="AF42">
-        <v>99</v>
-      </c>
-      <c r="AG42">
-        <v>371</v>
-      </c>
-      <c r="AH42">
-        <v>1171</v>
-      </c>
-      <c r="AI42">
-        <v>72</v>
-      </c>
-      <c r="AJ42">
-        <v>105</v>
-      </c>
-      <c r="AK42">
-        <v>591</v>
-      </c>
-      <c r="AL42">
-        <v>78</v>
-      </c>
-      <c r="AM42">
-        <v>84</v>
-      </c>
-      <c r="AN42">
-        <v>476</v>
-      </c>
-      <c r="AO42">
-        <v>59</v>
-      </c>
-      <c r="AP42">
-        <v>115</v>
-      </c>
-      <c r="AQ42">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="43" spans="1:43">
+    </row>
+    <row r="43" spans="1:22">
       <c r="A43" t="s">
         <v>44</v>
       </c>
       <c r="B43" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E43,H43,K43,N43,Q43,T43)</f>
         <v>489</v>
       </c>
       <c r="C43">
@@ -6406,77 +3732,13 @@
       <c r="V43">
         <v>1034</v>
       </c>
-      <c r="W43" s="2">
-        <f t="shared" si="1"/>
-        <v>489</v>
-      </c>
-      <c r="X43">
-        <v>110</v>
-      </c>
-      <c r="Y43">
-        <v>779</v>
-      </c>
-      <c r="Z43">
-        <v>102</v>
-      </c>
-      <c r="AA43">
-        <v>306</v>
-      </c>
-      <c r="AB43">
-        <v>979</v>
-      </c>
-      <c r="AC43">
-        <v>101</v>
-      </c>
-      <c r="AD43">
-        <v>215</v>
-      </c>
-      <c r="AE43">
-        <v>646</v>
-      </c>
-      <c r="AF43">
-        <v>97</v>
-      </c>
-      <c r="AG43">
-        <v>417</v>
-      </c>
-      <c r="AH43">
-        <v>1244</v>
-      </c>
-      <c r="AI43">
-        <v>76</v>
-      </c>
-      <c r="AJ43">
-        <v>68</v>
-      </c>
-      <c r="AK43">
-        <v>448</v>
-      </c>
-      <c r="AL43">
-        <v>62</v>
-      </c>
-      <c r="AM43">
-        <v>398</v>
-      </c>
-      <c r="AN43">
-        <v>1196</v>
-      </c>
-      <c r="AO43">
-        <v>51</v>
-      </c>
-      <c r="AP43">
-        <v>263</v>
-      </c>
-      <c r="AQ43">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="44" spans="1:43">
+    </row>
+    <row r="44" spans="1:22">
       <c r="A44" t="s">
         <v>38</v>
       </c>
       <c r="B44" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E44,H44,K44,N44,Q44,T44)</f>
         <v>514</v>
       </c>
       <c r="C44">
@@ -6539,77 +3801,13 @@
       <c r="V44">
         <v>501</v>
       </c>
-      <c r="W44" s="2">
-        <f t="shared" si="1"/>
-        <v>514</v>
-      </c>
-      <c r="X44">
-        <v>140</v>
-      </c>
-      <c r="Y44">
-        <v>840</v>
-      </c>
-      <c r="Z44">
-        <v>106</v>
-      </c>
-      <c r="AA44">
-        <v>152</v>
-      </c>
-      <c r="AB44">
-        <v>642</v>
-      </c>
-      <c r="AC44">
-        <v>93</v>
-      </c>
-      <c r="AD44">
-        <v>325</v>
-      </c>
-      <c r="AE44">
-        <v>910</v>
-      </c>
-      <c r="AF44">
-        <v>111</v>
-      </c>
-      <c r="AG44">
-        <v>167</v>
-      </c>
-      <c r="AH44">
-        <v>707</v>
-      </c>
-      <c r="AI44">
-        <v>63</v>
-      </c>
-      <c r="AJ44">
-        <v>270</v>
-      </c>
-      <c r="AK44">
-        <v>944</v>
-      </c>
-      <c r="AL44">
-        <v>76</v>
-      </c>
-      <c r="AM44">
-        <v>102</v>
-      </c>
-      <c r="AN44">
-        <v>541</v>
-      </c>
-      <c r="AO44">
-        <v>65</v>
-      </c>
-      <c r="AP44">
-        <v>54</v>
-      </c>
-      <c r="AQ44">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="45" spans="1:43">
+    </row>
+    <row r="45" spans="1:22">
       <c r="A45" t="s">
         <v>27</v>
       </c>
       <c r="B45" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E45,H45,K45,N45,Q45,T45)</f>
         <v>529</v>
       </c>
       <c r="C45">
@@ -6672,77 +3870,13 @@
       <c r="V45">
         <v>253</v>
       </c>
-      <c r="W45" s="2">
-        <f t="shared" si="1"/>
-        <v>529</v>
-      </c>
-      <c r="X45">
-        <v>95</v>
-      </c>
-      <c r="Y45">
-        <v>737</v>
-      </c>
-      <c r="Z45">
-        <v>106</v>
-      </c>
-      <c r="AA45">
-        <v>152</v>
-      </c>
-      <c r="AB45">
-        <v>642</v>
-      </c>
-      <c r="AC45">
-        <v>83</v>
-      </c>
-      <c r="AD45">
-        <v>471</v>
-      </c>
-      <c r="AE45">
-        <v>1226</v>
-      </c>
-      <c r="AF45">
-        <v>120</v>
-      </c>
-      <c r="AG45">
-        <v>73</v>
-      </c>
-      <c r="AH45">
-        <v>350</v>
-      </c>
-      <c r="AI45">
-        <v>63</v>
-      </c>
-      <c r="AJ45">
-        <v>270</v>
-      </c>
-      <c r="AK45">
-        <v>944</v>
-      </c>
-      <c r="AL45">
-        <v>84</v>
-      </c>
-      <c r="AM45">
-        <v>22</v>
-      </c>
-      <c r="AN45">
-        <v>215</v>
-      </c>
-      <c r="AO45">
-        <v>73</v>
-      </c>
-      <c r="AP45">
-        <v>13</v>
-      </c>
-      <c r="AQ45">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="46" spans="1:43">
+    </row>
+    <row r="46" spans="1:22">
       <c r="A46" t="s">
         <v>43</v>
       </c>
       <c r="B46" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E46,H46,K46,N46,Q46,T46)</f>
         <v>485</v>
       </c>
       <c r="C46">
@@ -6805,77 +3939,13 @@
       <c r="V46">
         <v>1140</v>
       </c>
-      <c r="W46" s="2">
-        <f t="shared" si="1"/>
-        <v>485</v>
-      </c>
-      <c r="X46">
-        <v>110</v>
-      </c>
-      <c r="Y46">
-        <v>779</v>
-      </c>
-      <c r="Z46">
-        <v>98</v>
-      </c>
-      <c r="AA46">
-        <v>455</v>
-      </c>
-      <c r="AB46">
-        <v>1255</v>
-      </c>
-      <c r="AC46">
-        <v>114</v>
-      </c>
-      <c r="AD46">
-        <v>62</v>
-      </c>
-      <c r="AE46">
-        <v>262</v>
-      </c>
-      <c r="AF46">
-        <v>88</v>
-      </c>
-      <c r="AG46">
-        <v>576</v>
-      </c>
-      <c r="AH46">
-        <v>1470</v>
-      </c>
-      <c r="AI46">
-        <v>72</v>
-      </c>
-      <c r="AJ46">
-        <v>105</v>
-      </c>
-      <c r="AK46">
-        <v>591</v>
-      </c>
-      <c r="AL46">
-        <v>65</v>
-      </c>
-      <c r="AM46">
-        <v>279</v>
-      </c>
-      <c r="AN46">
-        <v>1002</v>
-      </c>
-      <c r="AO46">
-        <v>48</v>
-      </c>
-      <c r="AP46">
-        <v>323</v>
-      </c>
-      <c r="AQ46">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="47" spans="1:43">
+    </row>
+    <row r="47" spans="1:22">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E47,H47,K47,N47,Q47,T47)</f>
         <v>495</v>
       </c>
       <c r="C47">
@@ -6938,77 +4008,13 @@
       <c r="V47">
         <v>912</v>
       </c>
-      <c r="W47" s="2">
-        <f t="shared" si="1"/>
-        <v>495</v>
-      </c>
-      <c r="X47">
-        <v>360</v>
-      </c>
-      <c r="Y47">
-        <v>1208</v>
-      </c>
-      <c r="Z47">
-        <v>101</v>
-      </c>
-      <c r="AA47">
-        <v>335</v>
-      </c>
-      <c r="AB47">
-        <v>1041</v>
-      </c>
-      <c r="AC47">
-        <v>96</v>
-      </c>
-      <c r="AD47">
-        <v>280</v>
-      </c>
-      <c r="AE47">
-        <v>816</v>
-      </c>
-      <c r="AF47">
-        <v>98</v>
-      </c>
-      <c r="AG47">
-        <v>386</v>
-      </c>
-      <c r="AH47">
-        <v>1206</v>
-      </c>
-      <c r="AI47">
-        <v>73</v>
-      </c>
-      <c r="AJ47">
-        <v>95</v>
-      </c>
-      <c r="AK47">
-        <v>552</v>
-      </c>
-      <c r="AL47">
-        <v>75</v>
-      </c>
-      <c r="AM47">
-        <v>129</v>
-      </c>
-      <c r="AN47">
-        <v>638</v>
-      </c>
-      <c r="AO47">
-        <v>52</v>
-      </c>
-      <c r="AP47">
-        <v>192</v>
-      </c>
-      <c r="AQ47">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="48" spans="1:43">
+    </row>
+    <row r="48" spans="1:22">
       <c r="A48" t="s">
         <v>11</v>
       </c>
       <c r="B48" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E48,H48,K48,N48,Q48,T48)</f>
         <v>495</v>
       </c>
       <c r="C48">
@@ -7071,77 +4077,13 @@
       <c r="V48">
         <v>912</v>
       </c>
-      <c r="W48" s="2">
-        <f t="shared" si="1"/>
-        <v>495</v>
-      </c>
-      <c r="X48">
-        <v>124</v>
-      </c>
-      <c r="Y48">
-        <v>813</v>
-      </c>
-      <c r="Z48">
-        <v>103</v>
-      </c>
-      <c r="AA48">
-        <v>258</v>
-      </c>
-      <c r="AB48">
-        <v>882</v>
-      </c>
-      <c r="AC48">
-        <v>114</v>
-      </c>
-      <c r="AD48">
-        <v>62</v>
-      </c>
-      <c r="AE48">
-        <v>262</v>
-      </c>
-      <c r="AF48">
-        <v>93</v>
-      </c>
-      <c r="AG48">
-        <v>485</v>
-      </c>
-      <c r="AH48">
-        <v>1349</v>
-      </c>
-      <c r="AI48">
-        <v>56</v>
-      </c>
-      <c r="AJ48">
-        <v>403</v>
-      </c>
-      <c r="AK48">
-        <v>1205</v>
-      </c>
-      <c r="AL48">
-        <v>77</v>
-      </c>
-      <c r="AM48">
-        <v>102</v>
-      </c>
-      <c r="AN48">
-        <v>541</v>
-      </c>
-      <c r="AO48">
-        <v>52</v>
-      </c>
-      <c r="AP48">
-        <v>192</v>
-      </c>
-      <c r="AQ48">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="49" spans="1:43">
+    </row>
+    <row r="49" spans="1:22">
       <c r="A49" t="s">
         <v>31</v>
       </c>
       <c r="B49" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E49,H49,K49,N49,Q49,T49)</f>
         <v>507</v>
       </c>
       <c r="C49">
@@ -7204,77 +4146,13 @@
       <c r="V49">
         <v>578</v>
       </c>
-      <c r="W49" s="2">
-        <f t="shared" si="1"/>
-        <v>507</v>
-      </c>
-      <c r="X49">
-        <v>92</v>
-      </c>
-      <c r="Y49">
-        <v>730</v>
-      </c>
-      <c r="Z49">
-        <v>98</v>
-      </c>
-      <c r="AA49">
-        <v>455</v>
-      </c>
-      <c r="AB49">
-        <v>1255</v>
-      </c>
-      <c r="AC49">
-        <v>99</v>
-      </c>
-      <c r="AD49">
-        <v>241</v>
-      </c>
-      <c r="AE49">
-        <v>710</v>
-      </c>
-      <c r="AF49">
-        <v>76</v>
-      </c>
-      <c r="AG49">
-        <v>744</v>
-      </c>
-      <c r="AH49">
-        <v>1694</v>
-      </c>
-      <c r="AI49">
-        <v>90</v>
-      </c>
-      <c r="AJ49">
-        <v>2</v>
-      </c>
-      <c r="AK49">
-        <v>63</v>
-      </c>
-      <c r="AL49">
-        <v>81</v>
-      </c>
-      <c r="AM49">
-        <v>38</v>
-      </c>
-      <c r="AN49">
-        <v>306</v>
-      </c>
-      <c r="AO49">
-        <v>63</v>
-      </c>
-      <c r="AP49">
-        <v>73</v>
-      </c>
-      <c r="AQ49">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="50" spans="1:43">
+    </row>
+    <row r="50" spans="1:22">
       <c r="A50" t="s">
         <v>47</v>
       </c>
       <c r="B50" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(E50,H50,K50,N50,Q50,T50)</f>
         <v>472</v>
       </c>
       <c r="C50">
@@ -7337,72 +4215,8 @@
       <c r="V50">
         <v>825</v>
       </c>
-      <c r="W50" s="2">
-        <f t="shared" si="1"/>
-        <v>472</v>
-      </c>
-      <c r="X50">
-        <v>365</v>
-      </c>
-      <c r="Y50">
-        <v>1214</v>
-      </c>
-      <c r="Z50">
-        <v>100</v>
-      </c>
-      <c r="AA50">
-        <v>367</v>
-      </c>
-      <c r="AB50">
-        <v>1104</v>
-      </c>
-      <c r="AC50">
-        <v>91</v>
-      </c>
-      <c r="AD50">
-        <v>365</v>
-      </c>
-      <c r="AE50">
-        <v>990</v>
-      </c>
-      <c r="AF50">
-        <v>90</v>
-      </c>
-      <c r="AG50">
-        <v>533</v>
-      </c>
-      <c r="AH50">
-        <v>1417</v>
-      </c>
-      <c r="AI50">
-        <v>69</v>
-      </c>
-      <c r="AJ50">
-        <v>146</v>
-      </c>
-      <c r="AK50">
-        <v>695</v>
-      </c>
-      <c r="AL50">
-        <v>66</v>
-      </c>
-      <c r="AM50">
-        <v>279</v>
-      </c>
-      <c r="AN50">
-        <v>1002</v>
-      </c>
-      <c r="AO50">
-        <v>56</v>
-      </c>
-      <c r="AP50">
-        <v>151</v>
-      </c>
-      <c r="AQ50">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="51" spans="1:43">
+    </row>
+    <row r="51" spans="1:22">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -7470,68 +4284,3540 @@
       <c r="V51">
         <v>1034</v>
       </c>
-      <c r="W51" s="2">
-        <f>SUM(Z51,AC51,AF51,AI51,AL51,AO51)</f>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A51">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B41B5F-6084-E94D-ACC5-87B91612A72E}">
+  <dimension ref="A1:V51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="22" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2">
+        <f>SUM(E2,H2,K2,N2,Q2,T2)</f>
+        <v>575</v>
+      </c>
+      <c r="C2">
+        <v>321</v>
+      </c>
+      <c r="D2">
+        <v>1158</v>
+      </c>
+      <c r="E2">
+        <v>108</v>
+      </c>
+      <c r="F2">
+        <v>91</v>
+      </c>
+      <c r="G2">
+        <v>485</v>
+      </c>
+      <c r="H2">
+        <v>126</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>60</v>
+      </c>
+      <c r="K2">
+        <v>120</v>
+      </c>
+      <c r="L2">
+        <v>73</v>
+      </c>
+      <c r="M2">
+        <v>350</v>
+      </c>
+      <c r="N2">
+        <v>90</v>
+      </c>
+      <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2">
+        <v>63</v>
+      </c>
+      <c r="Q2">
+        <v>79</v>
+      </c>
+      <c r="R2">
+        <v>60</v>
+      </c>
+      <c r="S2">
+        <v>395</v>
+      </c>
+      <c r="T2">
+        <v>52</v>
+      </c>
+      <c r="U2">
+        <v>192</v>
+      </c>
+      <c r="V2">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2">
+        <f>SUM(E3,H3,K3,N3,Q3,T3)</f>
+        <v>568</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>279</v>
+      </c>
+      <c r="E3">
+        <v>107</v>
+      </c>
+      <c r="F3">
+        <v>117</v>
+      </c>
+      <c r="G3">
+        <v>559</v>
+      </c>
+      <c r="H3">
+        <v>118</v>
+      </c>
+      <c r="I3">
+        <v>37</v>
+      </c>
+      <c r="J3">
+        <v>182</v>
+      </c>
+      <c r="K3">
+        <v>127</v>
+      </c>
+      <c r="L3">
+        <v>12</v>
+      </c>
+      <c r="M3">
+        <v>126</v>
+      </c>
+      <c r="N3">
+        <v>81</v>
+      </c>
+      <c r="O3">
+        <v>32</v>
+      </c>
+      <c r="P3">
+        <v>284</v>
+      </c>
+      <c r="Q3">
+        <v>80</v>
+      </c>
+      <c r="R3">
+        <v>60</v>
+      </c>
+      <c r="S3">
+        <v>395</v>
+      </c>
+      <c r="T3">
+        <v>55</v>
+      </c>
+      <c r="U3">
+        <v>151</v>
+      </c>
+      <c r="V3">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <f>SUM(E4,H4,K4,N4,Q4,T4)</f>
+        <v>588</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>219</v>
+      </c>
+      <c r="E4">
+        <v>104</v>
+      </c>
+      <c r="F4">
+        <v>224</v>
+      </c>
+      <c r="G4">
+        <v>808</v>
+      </c>
+      <c r="H4">
+        <v>142</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>101</v>
+      </c>
+      <c r="L4">
+        <v>331</v>
+      </c>
+      <c r="M4">
+        <v>1095</v>
+      </c>
+      <c r="N4">
+        <v>84</v>
+      </c>
+      <c r="O4">
+        <v>14</v>
+      </c>
+      <c r="P4">
+        <v>185</v>
+      </c>
+      <c r="Q4">
+        <v>90</v>
+      </c>
+      <c r="R4">
+        <v>7</v>
+      </c>
+      <c r="S4">
+        <v>58</v>
+      </c>
+      <c r="T4">
+        <v>67</v>
+      </c>
+      <c r="U4">
+        <v>37</v>
+      </c>
+      <c r="V4">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <f>SUM(E5,H5,K5,N5,Q5,T5)</f>
+        <v>557</v>
+      </c>
+      <c r="C5">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>394</v>
+      </c>
+      <c r="E5">
+        <v>102</v>
+      </c>
+      <c r="F5">
+        <v>306</v>
+      </c>
+      <c r="G5">
+        <v>979</v>
+      </c>
+      <c r="H5">
+        <v>117</v>
+      </c>
+      <c r="I5">
+        <v>41</v>
+      </c>
+      <c r="J5">
+        <v>197</v>
+      </c>
+      <c r="K5">
+        <v>111</v>
+      </c>
+      <c r="L5">
+        <v>167</v>
+      </c>
+      <c r="M5">
+        <v>707</v>
+      </c>
+      <c r="N5">
+        <v>90</v>
+      </c>
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
+        <v>63</v>
+      </c>
+      <c r="Q5">
+        <v>75</v>
+      </c>
+      <c r="R5">
+        <v>129</v>
+      </c>
+      <c r="S5">
+        <v>638</v>
+      </c>
+      <c r="T5">
+        <v>62</v>
+      </c>
+      <c r="U5">
+        <v>73</v>
+      </c>
+      <c r="V5">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2">
+        <f>SUM(E6,H6,K6,N6,Q6,T6)</f>
+        <v>559</v>
+      </c>
+      <c r="C6">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>494</v>
+      </c>
+      <c r="E6">
+        <v>104</v>
+      </c>
+      <c r="F6">
+        <v>224</v>
+      </c>
+      <c r="G6">
+        <v>808</v>
+      </c>
+      <c r="H6">
+        <v>110</v>
+      </c>
+      <c r="I6">
+        <v>104</v>
+      </c>
+      <c r="J6">
+        <v>363</v>
+      </c>
+      <c r="K6">
+        <v>124</v>
+      </c>
+      <c r="L6">
+        <v>29</v>
+      </c>
+      <c r="M6">
+        <v>200</v>
+      </c>
+      <c r="N6">
+        <v>82</v>
+      </c>
+      <c r="O6">
+        <v>22</v>
+      </c>
+      <c r="P6">
+        <v>248</v>
+      </c>
+      <c r="Q6">
+        <v>74</v>
+      </c>
+      <c r="R6">
+        <v>141</v>
+      </c>
+      <c r="S6">
+        <v>675</v>
+      </c>
+      <c r="T6">
+        <v>65</v>
+      </c>
+      <c r="U6">
+        <v>54</v>
+      </c>
+      <c r="V6">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2">
+        <f>SUM(E7,H7,K7,N7,Q7,T7)</f>
+        <v>547</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>414</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>367</v>
+      </c>
+      <c r="G7">
+        <v>1104</v>
+      </c>
+      <c r="H7">
+        <v>119</v>
+      </c>
+      <c r="I7">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>159</v>
+      </c>
+      <c r="K7">
+        <v>122</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>268</v>
+      </c>
+      <c r="N7">
+        <v>77</v>
+      </c>
+      <c r="O7">
+        <v>55</v>
+      </c>
+      <c r="P7">
+        <v>405</v>
+      </c>
+      <c r="Q7">
+        <v>73</v>
+      </c>
+      <c r="R7">
+        <v>141</v>
+      </c>
+      <c r="S7">
+        <v>675</v>
+      </c>
+      <c r="T7">
+        <v>56</v>
+      </c>
+      <c r="U7">
+        <v>151</v>
+      </c>
+      <c r="V7">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="2">
+        <f>SUM(E8,H8,K8,N8,Q8,T8)</f>
+        <v>544</v>
+      </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>394</v>
+      </c>
+      <c r="E8">
+        <v>108</v>
+      </c>
+      <c r="F8">
+        <v>91</v>
+      </c>
+      <c r="G8">
+        <v>485</v>
+      </c>
+      <c r="H8">
+        <v>119</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>159</v>
+      </c>
+      <c r="K8">
+        <v>121</v>
+      </c>
+      <c r="L8">
+        <v>60</v>
+      </c>
+      <c r="M8">
+        <v>311</v>
+      </c>
+      <c r="N8">
+        <v>70</v>
+      </c>
+      <c r="O8">
+        <v>136</v>
+      </c>
+      <c r="P8">
+        <v>672</v>
+      </c>
+      <c r="Q8">
+        <v>60</v>
+      </c>
+      <c r="R8">
+        <v>398</v>
+      </c>
+      <c r="S8">
+        <v>1196</v>
+      </c>
+      <c r="T8">
+        <v>66</v>
+      </c>
+      <c r="U8">
+        <v>37</v>
+      </c>
+      <c r="V8">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2">
+        <f>SUM(E9,H9,K9,N9,Q9,T9)</f>
+        <v>562</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>309</v>
+      </c>
+      <c r="E9">
+        <v>105</v>
+      </c>
+      <c r="F9">
+        <v>187</v>
+      </c>
+      <c r="G9">
+        <v>717</v>
+      </c>
+      <c r="H9">
+        <v>114</v>
+      </c>
+      <c r="I9">
+        <v>62</v>
+      </c>
+      <c r="J9">
+        <v>262</v>
+      </c>
+      <c r="K9">
+        <v>135</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>20</v>
+      </c>
+      <c r="N9">
+        <v>59</v>
+      </c>
+      <c r="O9">
+        <v>340</v>
+      </c>
+      <c r="P9">
+        <v>1091</v>
+      </c>
+      <c r="Q9">
+        <v>85</v>
+      </c>
+      <c r="R9">
+        <v>22</v>
+      </c>
+      <c r="S9">
+        <v>215</v>
+      </c>
+      <c r="T9">
+        <v>64</v>
+      </c>
+      <c r="U9">
+        <v>54</v>
+      </c>
+      <c r="V9">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2">
+        <f>SUM(E10,H10,K10,N10,Q10,T10)</f>
+        <v>544</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <v>309</v>
+      </c>
+      <c r="E10">
+        <v>119</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>41</v>
+      </c>
+      <c r="H10">
+        <v>114</v>
+      </c>
+      <c r="I10">
+        <v>62</v>
+      </c>
+      <c r="J10">
+        <v>262</v>
+      </c>
+      <c r="K10">
+        <v>96</v>
+      </c>
+      <c r="L10">
+        <v>438</v>
+      </c>
+      <c r="M10">
+        <v>1273</v>
+      </c>
+      <c r="N10">
+        <v>80</v>
+      </c>
+      <c r="O10">
+        <v>38</v>
+      </c>
+      <c r="P10">
+        <v>317</v>
+      </c>
+      <c r="Q10">
+        <v>79</v>
+      </c>
+      <c r="R10">
+        <v>60</v>
+      </c>
+      <c r="S10">
+        <v>395</v>
+      </c>
+      <c r="T10">
+        <v>56</v>
+      </c>
+      <c r="U10">
+        <v>151</v>
+      </c>
+      <c r="V10">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="2">
+        <f>SUM(E11,H11,K11,N11,Q11,T11)</f>
+        <v>537</v>
+      </c>
+      <c r="C11">
+        <v>72</v>
+      </c>
+      <c r="D11">
+        <v>669</v>
+      </c>
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>367</v>
+      </c>
+      <c r="G11">
+        <v>1104</v>
+      </c>
+      <c r="H11">
+        <v>111</v>
+      </c>
+      <c r="I11">
+        <v>89</v>
+      </c>
+      <c r="J11">
+        <v>330</v>
+      </c>
+      <c r="K11">
+        <v>126</v>
+      </c>
+      <c r="L11">
+        <v>17</v>
+      </c>
+      <c r="M11">
+        <v>147</v>
+      </c>
+      <c r="N11">
+        <v>69</v>
+      </c>
+      <c r="O11">
+        <v>146</v>
+      </c>
+      <c r="P11">
+        <v>695</v>
+      </c>
+      <c r="Q11">
+        <v>78</v>
+      </c>
+      <c r="R11">
+        <v>84</v>
+      </c>
+      <c r="S11">
+        <v>476</v>
+      </c>
+      <c r="T11">
+        <v>53</v>
+      </c>
+      <c r="U11">
+        <v>192</v>
+      </c>
+      <c r="V11">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2">
+        <f>SUM(E12,H12,K12,N12,Q12,T12)</f>
+        <v>542</v>
+      </c>
+      <c r="C12">
+        <v>72</v>
+      </c>
+      <c r="D12">
+        <v>669</v>
+      </c>
+      <c r="E12">
+        <v>99</v>
+      </c>
+      <c r="F12">
+        <v>412</v>
+      </c>
+      <c r="G12">
+        <v>1185</v>
+      </c>
+      <c r="H12">
+        <v>117</v>
+      </c>
+      <c r="I12">
+        <v>41</v>
+      </c>
+      <c r="J12">
+        <v>197</v>
+      </c>
+      <c r="K12">
+        <v>102</v>
+      </c>
+      <c r="L12">
+        <v>318</v>
+      </c>
+      <c r="M12">
+        <v>1059</v>
+      </c>
+      <c r="N12">
+        <v>87</v>
+      </c>
+      <c r="O12">
+        <v>9</v>
+      </c>
+      <c r="P12">
+        <v>120</v>
+      </c>
+      <c r="Q12">
+        <v>81</v>
+      </c>
+      <c r="R12">
+        <v>38</v>
+      </c>
+      <c r="S12">
+        <v>306</v>
+      </c>
+      <c r="T12">
+        <v>56</v>
+      </c>
+      <c r="U12">
+        <v>151</v>
+      </c>
+      <c r="V12">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="2">
+        <f>SUM(E13,H13,K13,N13,Q13,T13)</f>
+        <v>535</v>
+      </c>
+      <c r="C13">
+        <v>63</v>
+      </c>
+      <c r="D13">
+        <v>637</v>
+      </c>
+      <c r="E13">
+        <v>107</v>
+      </c>
+      <c r="F13">
+        <v>117</v>
+      </c>
+      <c r="G13">
+        <v>559</v>
+      </c>
+      <c r="H13">
+        <v>99</v>
+      </c>
+      <c r="I13">
+        <v>241</v>
+      </c>
+      <c r="J13">
+        <v>710</v>
+      </c>
+      <c r="K13">
+        <v>119</v>
+      </c>
+      <c r="L13">
+        <v>80</v>
+      </c>
+      <c r="M13">
+        <v>392</v>
+      </c>
+      <c r="N13">
+        <v>79</v>
+      </c>
+      <c r="O13">
+        <v>42</v>
+      </c>
+      <c r="P13">
+        <v>342</v>
+      </c>
+      <c r="Q13">
+        <v>76</v>
+      </c>
+      <c r="R13">
+        <v>102</v>
+      </c>
+      <c r="S13">
+        <v>541</v>
+      </c>
+      <c r="T13">
+        <v>55</v>
+      </c>
+      <c r="U13">
+        <v>151</v>
+      </c>
+      <c r="V13">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2">
+        <f>SUM(E14,H14,K14,N14,Q14,T14)</f>
+        <v>562</v>
+      </c>
+      <c r="C14">
+        <v>47</v>
+      </c>
+      <c r="D14">
+        <v>541</v>
+      </c>
+      <c r="E14">
+        <v>110</v>
+      </c>
+      <c r="F14">
+        <v>54</v>
+      </c>
+      <c r="G14">
+        <v>360</v>
+      </c>
+      <c r="H14">
+        <v>108</v>
+      </c>
+      <c r="I14">
+        <v>128</v>
+      </c>
+      <c r="J14">
+        <v>418</v>
+      </c>
+      <c r="K14">
+        <v>114</v>
+      </c>
+      <c r="L14">
+        <v>126</v>
+      </c>
+      <c r="M14">
+        <v>591</v>
+      </c>
+      <c r="N14">
+        <v>71</v>
+      </c>
+      <c r="O14">
+        <v>122</v>
+      </c>
+      <c r="P14">
+        <v>632</v>
+      </c>
+      <c r="Q14">
+        <v>94</v>
+      </c>
+      <c r="R14">
+        <v>3</v>
+      </c>
+      <c r="S14">
+        <v>23</v>
+      </c>
+      <c r="T14">
+        <v>65</v>
+      </c>
+      <c r="U14">
+        <v>54</v>
+      </c>
+      <c r="V14">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <f>SUM(E15,H15,K15,N15,Q15,T15)</f>
+        <v>548</v>
+      </c>
+      <c r="C15">
+        <v>35</v>
+      </c>
+      <c r="D15">
+        <v>479</v>
+      </c>
+      <c r="E15">
+        <v>97</v>
+      </c>
+      <c r="F15">
+        <v>490</v>
+      </c>
+      <c r="G15">
+        <v>1318</v>
+      </c>
+      <c r="H15">
+        <v>120</v>
+      </c>
+      <c r="I15">
+        <v>27</v>
+      </c>
+      <c r="J15">
+        <v>145</v>
+      </c>
+      <c r="K15">
+        <v>101</v>
+      </c>
+      <c r="L15">
+        <v>331</v>
+      </c>
+      <c r="M15">
+        <v>1095</v>
+      </c>
+      <c r="N15">
+        <v>84</v>
+      </c>
+      <c r="O15">
+        <v>14</v>
+      </c>
+      <c r="P15">
+        <v>185</v>
+      </c>
+      <c r="Q15">
+        <v>78</v>
+      </c>
+      <c r="R15">
+        <v>84</v>
+      </c>
+      <c r="S15">
+        <v>476</v>
+      </c>
+      <c r="T15">
+        <v>68</v>
+      </c>
+      <c r="U15">
+        <v>26</v>
+      </c>
+      <c r="V15">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2">
+        <f>SUM(E16,H16,K16,N16,Q16,T16)</f>
+        <v>543</v>
+      </c>
+      <c r="C16">
+        <v>87</v>
+      </c>
+      <c r="D16">
+        <v>720</v>
+      </c>
+      <c r="E16">
+        <v>95</v>
+      </c>
+      <c r="F16">
+        <v>569</v>
+      </c>
+      <c r="G16">
+        <v>1430</v>
+      </c>
+      <c r="H16">
+        <v>121</v>
+      </c>
+      <c r="I16">
+        <v>19</v>
+      </c>
+      <c r="J16">
+        <v>124</v>
+      </c>
+      <c r="K16">
+        <v>113</v>
+      </c>
+      <c r="L16">
+        <v>142</v>
+      </c>
+      <c r="M16">
+        <v>630</v>
+      </c>
+      <c r="N16">
+        <v>72</v>
+      </c>
+      <c r="O16">
+        <v>105</v>
+      </c>
+      <c r="P16">
+        <v>591</v>
+      </c>
+      <c r="Q16">
+        <v>82</v>
+      </c>
+      <c r="R16">
+        <v>38</v>
+      </c>
+      <c r="S16">
+        <v>306</v>
+      </c>
+      <c r="T16">
+        <v>60</v>
+      </c>
+      <c r="U16">
+        <v>94</v>
+      </c>
+      <c r="V16">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="2">
+        <f>SUM(E17,H17,K17,N17,Q17,T17)</f>
+        <v>523</v>
+      </c>
+      <c r="C17">
+        <v>47</v>
+      </c>
+      <c r="D17">
+        <v>541</v>
+      </c>
+      <c r="E17">
+        <v>115</v>
+      </c>
+      <c r="F17">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>123</v>
+      </c>
+      <c r="H17">
+        <v>117</v>
+      </c>
+      <c r="I17">
+        <v>41</v>
+      </c>
+      <c r="J17">
+        <v>197</v>
+      </c>
+      <c r="K17">
+        <v>111</v>
+      </c>
+      <c r="L17">
+        <v>167</v>
+      </c>
+      <c r="M17">
+        <v>707</v>
+      </c>
+      <c r="N17">
+        <v>58</v>
+      </c>
+      <c r="O17">
+        <v>358</v>
+      </c>
+      <c r="P17">
+        <v>1125</v>
+      </c>
+      <c r="Q17">
+        <v>62</v>
+      </c>
+      <c r="R17">
+        <v>398</v>
+      </c>
+      <c r="S17">
+        <v>1196</v>
+      </c>
+      <c r="T17">
+        <v>60</v>
+      </c>
+      <c r="U17">
+        <v>94</v>
+      </c>
+      <c r="V17">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="2">
+        <f>SUM(E18,H18,K18,N18,Q18,T18)</f>
+        <v>547</v>
+      </c>
+      <c r="C18">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>322</v>
+      </c>
+      <c r="E18">
+        <v>109</v>
+      </c>
+      <c r="F18">
+        <v>67</v>
+      </c>
+      <c r="G18">
+        <v>415</v>
+      </c>
+      <c r="H18">
+        <v>114</v>
+      </c>
+      <c r="I18">
+        <v>62</v>
+      </c>
+      <c r="J18">
+        <v>262</v>
+      </c>
+      <c r="K18">
+        <v>106</v>
+      </c>
+      <c r="L18">
+        <v>252</v>
+      </c>
+      <c r="M18">
+        <v>907</v>
+      </c>
+      <c r="N18">
+        <v>72</v>
+      </c>
+      <c r="O18">
+        <v>105</v>
+      </c>
+      <c r="P18">
+        <v>591</v>
+      </c>
+      <c r="Q18">
+        <v>78</v>
+      </c>
+      <c r="R18">
+        <v>84</v>
+      </c>
+      <c r="S18">
+        <v>476</v>
+      </c>
+      <c r="T18">
+        <v>68</v>
+      </c>
+      <c r="U18">
+        <v>26</v>
+      </c>
+      <c r="V18">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2">
+        <f>SUM(E19,H19,K19,N19,Q19,T19)</f>
+        <v>542</v>
+      </c>
+      <c r="C19">
+        <v>63</v>
+      </c>
+      <c r="D19">
+        <v>637</v>
+      </c>
+      <c r="E19">
+        <v>109</v>
+      </c>
+      <c r="F19">
+        <v>67</v>
+      </c>
+      <c r="G19">
+        <v>415</v>
+      </c>
+      <c r="H19">
+        <v>106</v>
+      </c>
+      <c r="I19">
+        <v>152</v>
+      </c>
+      <c r="J19">
+        <v>477</v>
+      </c>
+      <c r="K19">
+        <v>111</v>
+      </c>
+      <c r="L19">
+        <v>167</v>
+      </c>
+      <c r="M19">
+        <v>707</v>
+      </c>
+      <c r="N19">
+        <v>74</v>
+      </c>
+      <c r="O19">
+        <v>84</v>
+      </c>
+      <c r="P19">
+        <v>513</v>
+      </c>
+      <c r="Q19">
+        <v>82</v>
+      </c>
+      <c r="R19">
+        <v>38</v>
+      </c>
+      <c r="S19">
+        <v>306</v>
+      </c>
+      <c r="T19">
+        <v>60</v>
+      </c>
+      <c r="U19">
+        <v>94</v>
+      </c>
+      <c r="V19">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2">
+        <f>SUM(E20,H20,K20,N20,Q20,T20)</f>
+        <v>535</v>
+      </c>
+      <c r="C20">
+        <v>52</v>
+      </c>
+      <c r="D20">
+        <v>564</v>
+      </c>
+      <c r="E20">
+        <v>109</v>
+      </c>
+      <c r="F20">
+        <v>67</v>
+      </c>
+      <c r="G20">
+        <v>415</v>
+      </c>
+      <c r="H20">
+        <v>103</v>
+      </c>
+      <c r="I20">
+        <v>182</v>
+      </c>
+      <c r="J20">
+        <v>576</v>
+      </c>
+      <c r="K20">
+        <v>123</v>
+      </c>
+      <c r="L20">
+        <v>36</v>
+      </c>
+      <c r="M20">
+        <v>233</v>
+      </c>
+      <c r="N20">
+        <v>63</v>
+      </c>
+      <c r="O20">
+        <v>270</v>
+      </c>
+      <c r="P20">
+        <v>944</v>
+      </c>
+      <c r="Q20">
+        <v>62</v>
+      </c>
+      <c r="R20">
+        <v>398</v>
+      </c>
+      <c r="S20">
+        <v>1196</v>
+      </c>
+      <c r="T20">
+        <v>75</v>
+      </c>
+      <c r="U20">
+        <v>9</v>
+      </c>
+      <c r="V20">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2">
+        <f>SUM(E21,H21,K21,N21,Q21,T21)</f>
+        <v>568</v>
+      </c>
+      <c r="C21">
+        <v>26</v>
+      </c>
+      <c r="D21">
+        <v>438</v>
+      </c>
+      <c r="E21">
+        <v>95</v>
+      </c>
+      <c r="F21">
+        <v>569</v>
+      </c>
+      <c r="G21">
+        <v>1430</v>
+      </c>
+      <c r="H21">
+        <v>111</v>
+      </c>
+      <c r="I21">
+        <v>89</v>
+      </c>
+      <c r="J21">
+        <v>330</v>
+      </c>
+      <c r="K21">
+        <v>112</v>
+      </c>
+      <c r="L21">
+        <v>150</v>
+      </c>
+      <c r="M21">
+        <v>664</v>
+      </c>
+      <c r="N21">
+        <v>79</v>
+      </c>
+      <c r="O21">
+        <v>42</v>
+      </c>
+      <c r="P21">
+        <v>342</v>
+      </c>
+      <c r="Q21">
+        <v>96</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>7</v>
+      </c>
+      <c r="T21">
+        <v>75</v>
+      </c>
+      <c r="U21">
+        <v>9</v>
+      </c>
+      <c r="V21">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="2">
+        <f>SUM(E22,H22,K22,N22,Q22,T22)</f>
+        <v>513</v>
+      </c>
+      <c r="C22">
+        <v>289</v>
+      </c>
+      <c r="D22">
+        <v>1117</v>
+      </c>
+      <c r="E22">
+        <v>102</v>
+      </c>
+      <c r="F22">
+        <v>306</v>
+      </c>
+      <c r="G22">
+        <v>979</v>
+      </c>
+      <c r="H22">
+        <v>111</v>
+      </c>
+      <c r="I22">
+        <v>89</v>
+      </c>
+      <c r="J22">
+        <v>330</v>
+      </c>
+      <c r="K22">
+        <v>114</v>
+      </c>
+      <c r="L22">
+        <v>126</v>
+      </c>
+      <c r="M22">
+        <v>591</v>
+      </c>
+      <c r="N22">
+        <v>70</v>
+      </c>
+      <c r="O22">
+        <v>136</v>
+      </c>
+      <c r="P22">
+        <v>672</v>
+      </c>
+      <c r="Q22">
+        <v>65</v>
+      </c>
+      <c r="R22">
+        <v>279</v>
+      </c>
+      <c r="S22">
+        <v>1002</v>
+      </c>
+      <c r="T22">
+        <v>51</v>
+      </c>
+      <c r="U22">
+        <v>263</v>
+      </c>
+      <c r="V22">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="2">
+        <f>SUM(E23,H23,K23,N23,Q23,T23)</f>
+        <v>527</v>
+      </c>
+      <c r="C23">
+        <v>124</v>
+      </c>
+      <c r="D23">
+        <v>813</v>
+      </c>
+      <c r="E23">
+        <v>105</v>
+      </c>
+      <c r="F23">
+        <v>187</v>
+      </c>
+      <c r="G23">
+        <v>717</v>
+      </c>
+      <c r="H23">
+        <v>121</v>
+      </c>
+      <c r="I23">
+        <v>19</v>
+      </c>
+      <c r="J23">
+        <v>124</v>
+      </c>
+      <c r="K23">
+        <v>99</v>
+      </c>
+      <c r="L23">
+        <v>371</v>
+      </c>
+      <c r="M23">
+        <v>1171</v>
+      </c>
+      <c r="N23">
+        <v>71</v>
+      </c>
+      <c r="O23">
+        <v>122</v>
+      </c>
+      <c r="P23">
+        <v>632</v>
+      </c>
+      <c r="Q23">
+        <v>70</v>
+      </c>
+      <c r="R23">
+        <v>206</v>
+      </c>
+      <c r="S23">
+        <v>852</v>
+      </c>
+      <c r="T23">
+        <v>61</v>
+      </c>
+      <c r="U23">
+        <v>94</v>
+      </c>
+      <c r="V23">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="2">
+        <f>SUM(E24,H24,K24,N24,Q24,T24)</f>
+        <v>535</v>
+      </c>
+      <c r="C24">
+        <v>163</v>
+      </c>
+      <c r="D24">
+        <v>889</v>
+      </c>
+      <c r="E24">
+        <v>102</v>
+      </c>
+      <c r="F24">
+        <v>306</v>
+      </c>
+      <c r="G24">
+        <v>979</v>
+      </c>
+      <c r="H24">
+        <v>123</v>
+      </c>
+      <c r="I24">
+        <v>15</v>
+      </c>
+      <c r="J24">
+        <v>101</v>
+      </c>
+      <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
+        <v>353</v>
+      </c>
+      <c r="M24">
+        <v>1137</v>
+      </c>
+      <c r="N24">
+        <v>68</v>
+      </c>
+      <c r="O24">
+        <v>169</v>
+      </c>
+      <c r="P24">
+        <v>740</v>
+      </c>
+      <c r="Q24">
+        <v>80</v>
+      </c>
+      <c r="R24">
+        <v>60</v>
+      </c>
+      <c r="S24">
+        <v>395</v>
+      </c>
+      <c r="T24">
+        <v>62</v>
+      </c>
+      <c r="U24">
+        <v>73</v>
+      </c>
+      <c r="V24">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <f>SUM(E25,H25,K25,N25,Q25,T25)</f>
+        <v>514</v>
+      </c>
+      <c r="C25">
+        <v>98</v>
+      </c>
+      <c r="D25">
+        <v>744</v>
+      </c>
+      <c r="E25">
+        <v>101</v>
+      </c>
+      <c r="F25">
+        <v>335</v>
+      </c>
+      <c r="G25">
+        <v>1041</v>
+      </c>
+      <c r="H25">
+        <v>111</v>
+      </c>
+      <c r="I25">
+        <v>89</v>
+      </c>
+      <c r="J25">
+        <v>330</v>
+      </c>
+      <c r="K25">
+        <v>116</v>
+      </c>
+      <c r="L25">
+        <v>109</v>
+      </c>
+      <c r="M25">
+        <v>514</v>
+      </c>
+      <c r="N25">
+        <v>64</v>
+      </c>
+      <c r="O25">
+        <v>245</v>
+      </c>
+      <c r="P25">
+        <v>901</v>
+      </c>
+      <c r="Q25">
+        <v>70</v>
+      </c>
+      <c r="R25">
+        <v>206</v>
+      </c>
+      <c r="S25">
+        <v>852</v>
+      </c>
+      <c r="T25">
+        <v>52</v>
+      </c>
+      <c r="U25">
+        <v>192</v>
+      </c>
+      <c r="V25">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="2">
+        <f>SUM(E26,H26,K26,N26,Q26,T26)</f>
+        <v>538</v>
+      </c>
+      <c r="C26">
+        <v>37</v>
+      </c>
+      <c r="D26">
+        <v>494</v>
+      </c>
+      <c r="E26">
+        <v>104</v>
+      </c>
+      <c r="F26">
+        <v>224</v>
+      </c>
+      <c r="G26">
+        <v>808</v>
+      </c>
+      <c r="H26">
+        <v>95</v>
+      </c>
+      <c r="I26">
+        <v>296</v>
+      </c>
+      <c r="J26">
+        <v>848</v>
+      </c>
+      <c r="K26">
+        <v>128</v>
+      </c>
+      <c r="L26">
+        <v>11</v>
+      </c>
+      <c r="M26">
+        <v>108</v>
+      </c>
+      <c r="N26">
+        <v>63</v>
+      </c>
+      <c r="O26">
+        <v>270</v>
+      </c>
+      <c r="P26">
+        <v>944</v>
+      </c>
+      <c r="Q26">
+        <v>82</v>
+      </c>
+      <c r="R26">
+        <v>38</v>
+      </c>
+      <c r="S26">
+        <v>306</v>
+      </c>
+      <c r="T26">
+        <v>66</v>
+      </c>
+      <c r="U26">
+        <v>37</v>
+      </c>
+      <c r="V26">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="2">
+        <f>SUM(E27,H27,K27,N27,Q27,T27)</f>
+        <v>515</v>
+      </c>
+      <c r="C27">
+        <v>159</v>
+      </c>
+      <c r="D27">
+        <v>878</v>
+      </c>
+      <c r="E27">
+        <v>94</v>
+      </c>
+      <c r="F27">
+        <v>604</v>
+      </c>
+      <c r="G27">
+        <v>1485</v>
+      </c>
+      <c r="H27">
+        <v>115</v>
+      </c>
+      <c r="I27">
+        <v>58</v>
+      </c>
+      <c r="J27">
+        <v>236</v>
+      </c>
+      <c r="K27">
+        <v>112</v>
+      </c>
+      <c r="L27">
+        <v>150</v>
+      </c>
+      <c r="M27">
+        <v>664</v>
+      </c>
+      <c r="N27">
+        <v>68</v>
+      </c>
+      <c r="O27">
+        <v>169</v>
+      </c>
+      <c r="P27">
+        <v>740</v>
+      </c>
+      <c r="Q27">
+        <v>69</v>
+      </c>
+      <c r="R27">
+        <v>206</v>
+      </c>
+      <c r="S27">
+        <v>852</v>
+      </c>
+      <c r="T27">
+        <v>57</v>
+      </c>
+      <c r="U27">
+        <v>115</v>
+      </c>
+      <c r="V27">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="2">
+        <f>SUM(E28,H28,K28,N28,Q28,T28)</f>
+        <v>528</v>
+      </c>
+      <c r="C28">
+        <v>40</v>
+      </c>
+      <c r="D28">
+        <v>505</v>
+      </c>
+      <c r="E28">
+        <v>95</v>
+      </c>
+      <c r="F28">
+        <v>569</v>
+      </c>
+      <c r="G28">
+        <v>1430</v>
+      </c>
+      <c r="H28">
+        <v>92</v>
+      </c>
+      <c r="I28">
+        <v>343</v>
+      </c>
+      <c r="J28">
+        <v>950</v>
+      </c>
+      <c r="K28">
+        <v>119</v>
+      </c>
+      <c r="L28">
+        <v>80</v>
+      </c>
+      <c r="M28">
+        <v>392</v>
+      </c>
+      <c r="N28">
+        <v>82</v>
+      </c>
+      <c r="O28">
+        <v>22</v>
+      </c>
+      <c r="P28">
+        <v>248</v>
+      </c>
+      <c r="Q28">
+        <v>74</v>
+      </c>
+      <c r="R28">
+        <v>141</v>
+      </c>
+      <c r="S28">
+        <v>675</v>
+      </c>
+      <c r="T28">
+        <v>66</v>
+      </c>
+      <c r="U28">
+        <v>37</v>
+      </c>
+      <c r="V28">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="2">
+        <f>SUM(E29,H29,K29,N29,Q29,T29)</f>
+        <v>508</v>
+      </c>
+      <c r="C29">
+        <v>124</v>
+      </c>
+      <c r="D29">
+        <v>813</v>
+      </c>
+      <c r="E29">
+        <v>103</v>
+      </c>
+      <c r="F29">
+        <v>258</v>
+      </c>
+      <c r="G29">
+        <v>882</v>
+      </c>
+      <c r="H29">
+        <v>103</v>
+      </c>
+      <c r="I29">
+        <v>182</v>
+      </c>
+      <c r="J29">
+        <v>576</v>
+      </c>
+      <c r="K29">
+        <v>120</v>
+      </c>
+      <c r="L29">
+        <v>73</v>
+      </c>
+      <c r="M29">
+        <v>350</v>
+      </c>
+      <c r="N29">
+        <v>61</v>
+      </c>
+      <c r="O29">
+        <v>303</v>
+      </c>
+      <c r="P29">
+        <v>1011</v>
+      </c>
+      <c r="Q29">
+        <v>78</v>
+      </c>
+      <c r="R29">
+        <v>84</v>
+      </c>
+      <c r="S29">
+        <v>476</v>
+      </c>
+      <c r="T29">
+        <v>43</v>
+      </c>
+      <c r="U29">
+        <v>448</v>
+      </c>
+      <c r="V29">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="2">
+        <f>SUM(E30,H30,K30,N30,Q30,T30)</f>
+        <v>519</v>
+      </c>
+      <c r="C30">
+        <v>167</v>
+      </c>
+      <c r="D30">
+        <v>897</v>
+      </c>
+      <c r="E30">
+        <v>99</v>
+      </c>
+      <c r="F30">
+        <v>412</v>
+      </c>
+      <c r="G30">
+        <v>1185</v>
+      </c>
+      <c r="H30">
+        <v>104</v>
+      </c>
+      <c r="I30">
+        <v>172</v>
+      </c>
+      <c r="J30">
+        <v>540</v>
+      </c>
+      <c r="K30">
+        <v>109</v>
+      </c>
+      <c r="L30">
+        <v>193</v>
+      </c>
+      <c r="M30">
+        <v>780</v>
+      </c>
+      <c r="N30">
+        <v>74</v>
+      </c>
+      <c r="O30">
+        <v>84</v>
+      </c>
+      <c r="P30">
+        <v>513</v>
+      </c>
+      <c r="Q30">
+        <v>70</v>
+      </c>
+      <c r="R30">
+        <v>206</v>
+      </c>
+      <c r="S30">
+        <v>852</v>
+      </c>
+      <c r="T30">
+        <v>63</v>
+      </c>
+      <c r="U30">
+        <v>73</v>
+      </c>
+      <c r="V30">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="2">
+        <f>SUM(E31,H31,K31,N31,Q31,T31)</f>
+        <v>532</v>
+      </c>
+      <c r="C31">
+        <v>98</v>
+      </c>
+      <c r="D31">
+        <v>744</v>
+      </c>
+      <c r="E31">
+        <v>107</v>
+      </c>
+      <c r="F31">
+        <v>117</v>
+      </c>
+      <c r="G31">
+        <v>559</v>
+      </c>
+      <c r="H31">
+        <v>121</v>
+      </c>
+      <c r="I31">
+        <v>19</v>
+      </c>
+      <c r="J31">
+        <v>124</v>
+      </c>
+      <c r="K31">
+        <v>96</v>
+      </c>
+      <c r="L31">
+        <v>438</v>
+      </c>
+      <c r="M31">
+        <v>1273</v>
+      </c>
+      <c r="N31">
+        <v>62</v>
+      </c>
+      <c r="O31">
+        <v>285</v>
+      </c>
+      <c r="P31">
+        <v>971</v>
+      </c>
+      <c r="Q31">
+        <v>79</v>
+      </c>
+      <c r="R31">
+        <v>60</v>
+      </c>
+      <c r="S31">
+        <v>395</v>
+      </c>
+      <c r="T31">
+        <v>67</v>
+      </c>
+      <c r="U31">
+        <v>37</v>
+      </c>
+      <c r="V31">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="2">
+        <f>SUM(E32,H32,K32,N32,Q32,T32)</f>
+        <v>522</v>
+      </c>
+      <c r="C32">
+        <v>167</v>
+      </c>
+      <c r="D32">
+        <v>897</v>
+      </c>
+      <c r="E32">
+        <v>84</v>
+      </c>
+      <c r="F32">
+        <v>803</v>
+      </c>
+      <c r="G32">
+        <v>1753</v>
+      </c>
+      <c r="H32">
+        <v>111</v>
+      </c>
+      <c r="I32">
+        <v>89</v>
+      </c>
+      <c r="J32">
+        <v>330</v>
+      </c>
+      <c r="K32">
+        <v>108</v>
+      </c>
+      <c r="L32">
+        <v>206</v>
+      </c>
+      <c r="M32">
+        <v>814</v>
+      </c>
+      <c r="N32">
+        <v>83</v>
+      </c>
+      <c r="O32">
+        <v>19</v>
+      </c>
+      <c r="P32">
+        <v>214</v>
+      </c>
+      <c r="Q32">
+        <v>80</v>
+      </c>
+      <c r="R32">
+        <v>60</v>
+      </c>
+      <c r="S32">
+        <v>395</v>
+      </c>
+      <c r="T32">
+        <v>56</v>
+      </c>
+      <c r="U32">
+        <v>151</v>
+      </c>
+      <c r="V32">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
+      <c r="A33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="2">
+        <f>SUM(E33,H33,K33,N33,Q33,T33)</f>
+        <v>518</v>
+      </c>
+      <c r="C33">
+        <v>62</v>
+      </c>
+      <c r="D33">
+        <v>629</v>
+      </c>
+      <c r="E33">
+        <v>108</v>
+      </c>
+      <c r="F33">
+        <v>91</v>
+      </c>
+      <c r="G33">
+        <v>485</v>
+      </c>
+      <c r="H33">
+        <v>105</v>
+      </c>
+      <c r="I33">
+        <v>160</v>
+      </c>
+      <c r="J33">
+        <v>507</v>
+      </c>
+      <c r="K33">
+        <v>106</v>
+      </c>
+      <c r="L33">
+        <v>252</v>
+      </c>
+      <c r="M33">
+        <v>907</v>
+      </c>
+      <c r="N33">
+        <v>66</v>
+      </c>
+      <c r="O33">
+        <v>206</v>
+      </c>
+      <c r="P33">
+        <v>828</v>
+      </c>
+      <c r="Q33">
+        <v>81</v>
+      </c>
+      <c r="R33">
+        <v>38</v>
+      </c>
+      <c r="S33">
+        <v>306</v>
+      </c>
+      <c r="T33">
+        <v>52</v>
+      </c>
+      <c r="U33">
+        <v>192</v>
+      </c>
+      <c r="V33">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="2">
+        <f>SUM(E34,H34,K34,N34,Q34,T34)</f>
+        <v>506</v>
+      </c>
+      <c r="C34">
+        <v>44</v>
+      </c>
+      <c r="D34">
+        <v>524</v>
+      </c>
+      <c r="E34">
+        <v>110</v>
+      </c>
+      <c r="F34">
+        <v>54</v>
+      </c>
+      <c r="G34">
+        <v>360</v>
+      </c>
+      <c r="H34">
+        <v>91</v>
+      </c>
+      <c r="I34">
+        <v>365</v>
+      </c>
+      <c r="J34">
+        <v>990</v>
+      </c>
+      <c r="K34">
+        <v>121</v>
+      </c>
+      <c r="L34">
+        <v>60</v>
+      </c>
+      <c r="M34">
+        <v>311</v>
+      </c>
+      <c r="N34">
+        <v>63</v>
+      </c>
+      <c r="O34">
+        <v>270</v>
+      </c>
+      <c r="P34">
+        <v>944</v>
+      </c>
+      <c r="Q34">
+        <v>60</v>
+      </c>
+      <c r="R34">
+        <v>398</v>
+      </c>
+      <c r="S34">
+        <v>1196</v>
+      </c>
+      <c r="T34">
+        <v>61</v>
+      </c>
+      <c r="U34">
+        <v>94</v>
+      </c>
+      <c r="V34">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="2">
+        <f>SUM(E35,H35,K35,N35,Q35,T35)</f>
+        <v>497</v>
+      </c>
+      <c r="C35">
+        <v>163</v>
+      </c>
+      <c r="D35">
+        <v>889</v>
+      </c>
+      <c r="E35">
+        <v>105</v>
+      </c>
+      <c r="F35">
+        <v>187</v>
+      </c>
+      <c r="G35">
+        <v>717</v>
+      </c>
+      <c r="H35">
+        <v>107</v>
+      </c>
+      <c r="I35">
+        <v>140</v>
+      </c>
+      <c r="J35">
+        <v>451</v>
+      </c>
+      <c r="K35">
+        <v>106</v>
+      </c>
+      <c r="L35">
+        <v>252</v>
+      </c>
+      <c r="M35">
+        <v>907</v>
+      </c>
+      <c r="N35">
+        <v>66</v>
+      </c>
+      <c r="O35">
+        <v>206</v>
+      </c>
+      <c r="P35">
+        <v>828</v>
+      </c>
+      <c r="Q35">
+        <v>64</v>
+      </c>
+      <c r="R35">
+        <v>349</v>
+      </c>
+      <c r="S35">
+        <v>1115</v>
+      </c>
+      <c r="T35">
+        <v>49</v>
+      </c>
+      <c r="U35">
+        <v>263</v>
+      </c>
+      <c r="V35">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="2">
+        <f>SUM(E36,H36,K36,N36,Q36,T36)</f>
+        <v>505</v>
+      </c>
+      <c r="C36">
+        <v>145</v>
+      </c>
+      <c r="D36">
+        <v>847</v>
+      </c>
+      <c r="E36">
+        <v>102</v>
+      </c>
+      <c r="F36">
+        <v>306</v>
+      </c>
+      <c r="G36">
+        <v>979</v>
+      </c>
+      <c r="H36">
+        <v>114</v>
+      </c>
+      <c r="I36">
+        <v>62</v>
+      </c>
+      <c r="J36">
+        <v>262</v>
+      </c>
+      <c r="K36">
+        <v>117</v>
+      </c>
+      <c r="L36">
+        <v>95</v>
+      </c>
+      <c r="M36">
+        <v>471</v>
+      </c>
+      <c r="N36">
+        <v>51</v>
+      </c>
+      <c r="O36">
+        <v>508</v>
+      </c>
+      <c r="P36">
+        <v>1354</v>
+      </c>
+      <c r="Q36">
+        <v>67</v>
+      </c>
+      <c r="R36">
+        <v>279</v>
+      </c>
+      <c r="S36">
+        <v>1002</v>
+      </c>
+      <c r="T36">
+        <v>54</v>
+      </c>
+      <c r="U36">
+        <v>192</v>
+      </c>
+      <c r="V36">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22">
+      <c r="A37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="2">
+        <f>SUM(E37,H37,K37,N37,Q37,T37)</f>
+        <v>514</v>
+      </c>
+      <c r="C37">
+        <v>124</v>
+      </c>
+      <c r="D37">
+        <v>813</v>
+      </c>
+      <c r="E37">
+        <v>95</v>
+      </c>
+      <c r="F37">
+        <v>569</v>
+      </c>
+      <c r="G37">
+        <v>1430</v>
+      </c>
+      <c r="H37">
+        <v>114</v>
+      </c>
+      <c r="I37">
+        <v>62</v>
+      </c>
+      <c r="J37">
+        <v>262</v>
+      </c>
+      <c r="K37">
+        <v>110</v>
+      </c>
+      <c r="L37">
+        <v>181</v>
+      </c>
+      <c r="M37">
+        <v>740</v>
+      </c>
+      <c r="N37">
+        <v>65</v>
+      </c>
+      <c r="O37">
+        <v>226</v>
+      </c>
+      <c r="P37">
+        <v>867</v>
+      </c>
+      <c r="Q37">
+        <v>68</v>
+      </c>
+      <c r="R37">
+        <v>206</v>
+      </c>
+      <c r="S37">
+        <v>852</v>
+      </c>
+      <c r="T37">
+        <v>62</v>
+      </c>
+      <c r="U37">
+        <v>73</v>
+      </c>
+      <c r="V37">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
+      <c r="A38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="2">
+        <f>SUM(E38,H38,K38,N38,Q38,T38)</f>
+        <v>497</v>
+      </c>
+      <c r="C38">
+        <v>148</v>
+      </c>
+      <c r="D38">
+        <v>855</v>
+      </c>
+      <c r="E38">
+        <v>113</v>
+      </c>
+      <c r="F38">
+        <v>25</v>
+      </c>
+      <c r="G38">
+        <v>193</v>
+      </c>
+      <c r="H38">
+        <v>103</v>
+      </c>
+      <c r="I38">
+        <v>182</v>
+      </c>
+      <c r="J38">
+        <v>576</v>
+      </c>
+      <c r="K38">
+        <v>115</v>
+      </c>
+      <c r="L38">
+        <v>114</v>
+      </c>
+      <c r="M38">
+        <v>544</v>
+      </c>
+      <c r="N38">
+        <v>51</v>
+      </c>
+      <c r="O38">
+        <v>508</v>
+      </c>
+      <c r="P38">
+        <v>1354</v>
+      </c>
+      <c r="Q38">
+        <v>64</v>
+      </c>
+      <c r="R38">
+        <v>349</v>
+      </c>
+      <c r="S38">
+        <v>1115</v>
+      </c>
+      <c r="T38">
+        <v>51</v>
+      </c>
+      <c r="U38">
+        <v>263</v>
+      </c>
+      <c r="V38">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
+      <c r="A39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="2">
+        <f>SUM(E39,H39,K39,N39,Q39,T39)</f>
+        <v>543</v>
+      </c>
+      <c r="C39">
+        <v>68</v>
+      </c>
+      <c r="D39">
+        <v>646</v>
+      </c>
+      <c r="E39">
+        <v>109</v>
+      </c>
+      <c r="F39">
+        <v>67</v>
+      </c>
+      <c r="G39">
+        <v>415</v>
+      </c>
+      <c r="H39">
+        <v>95</v>
+      </c>
+      <c r="I39">
+        <v>296</v>
+      </c>
+      <c r="J39">
+        <v>848</v>
+      </c>
+      <c r="K39">
+        <v>109</v>
+      </c>
+      <c r="L39">
+        <v>193</v>
+      </c>
+      <c r="M39">
+        <v>780</v>
+      </c>
+      <c r="N39">
+        <v>69</v>
+      </c>
+      <c r="O39">
+        <v>146</v>
+      </c>
+      <c r="P39">
+        <v>695</v>
+      </c>
+      <c r="Q39">
+        <v>78</v>
+      </c>
+      <c r="R39">
+        <v>84</v>
+      </c>
+      <c r="S39">
+        <v>476</v>
+      </c>
+      <c r="T39">
+        <v>83</v>
+      </c>
+      <c r="U39">
+        <v>3</v>
+      </c>
+      <c r="V39">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
+      <c r="A40" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="2">
+        <f>SUM(E40,H40,K40,N40,Q40,T40)</f>
+        <v>519</v>
+      </c>
+      <c r="C40">
+        <v>140</v>
+      </c>
+      <c r="D40">
+        <v>840</v>
+      </c>
+      <c r="E40">
+        <v>108</v>
+      </c>
+      <c r="F40">
+        <v>91</v>
+      </c>
+      <c r="G40">
+        <v>485</v>
+      </c>
+      <c r="H40">
+        <v>92</v>
+      </c>
+      <c r="I40">
+        <v>343</v>
+      </c>
+      <c r="J40">
+        <v>950</v>
+      </c>
+      <c r="K40">
+        <v>112</v>
+      </c>
+      <c r="L40">
+        <v>150</v>
+      </c>
+      <c r="M40">
+        <v>664</v>
+      </c>
+      <c r="N40">
+        <v>69</v>
+      </c>
+      <c r="O40">
+        <v>146</v>
+      </c>
+      <c r="P40">
+        <v>695</v>
+      </c>
+      <c r="Q40">
+        <v>76</v>
+      </c>
+      <c r="R40">
+        <v>102</v>
+      </c>
+      <c r="S40">
+        <v>541</v>
+      </c>
+      <c r="T40">
+        <v>62</v>
+      </c>
+      <c r="U40">
+        <v>73</v>
+      </c>
+      <c r="V40">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
+      <c r="A41" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="2">
+        <f>SUM(E41,H41,K41,N41,Q41,T41)</f>
+        <v>529</v>
+      </c>
+      <c r="C41">
+        <v>81</v>
+      </c>
+      <c r="D41">
+        <v>707</v>
+      </c>
+      <c r="E41">
+        <v>109</v>
+      </c>
+      <c r="F41">
+        <v>67</v>
+      </c>
+      <c r="G41">
+        <v>415</v>
+      </c>
+      <c r="H41">
+        <v>101</v>
+      </c>
+      <c r="I41">
+        <v>215</v>
+      </c>
+      <c r="J41">
+        <v>646</v>
+      </c>
+      <c r="K41">
+        <v>95</v>
+      </c>
+      <c r="L41">
+        <v>456</v>
+      </c>
+      <c r="M41">
+        <v>1300</v>
+      </c>
+      <c r="N41">
+        <v>72</v>
+      </c>
+      <c r="O41">
+        <v>105</v>
+      </c>
+      <c r="P41">
+        <v>591</v>
+      </c>
+      <c r="Q41">
+        <v>92</v>
+      </c>
+      <c r="R41">
+        <v>5</v>
+      </c>
+      <c r="S41">
+        <v>43</v>
+      </c>
+      <c r="T41">
+        <v>60</v>
+      </c>
+      <c r="U41">
+        <v>94</v>
+      </c>
+      <c r="V41">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="2">
+        <f>SUM(E42,H42,K42,N42,Q42,T42)</f>
+        <v>514</v>
+      </c>
+      <c r="C42">
+        <v>419</v>
+      </c>
+      <c r="D42">
+        <v>1289</v>
+      </c>
+      <c r="E42">
+        <v>104</v>
+      </c>
+      <c r="F42">
+        <v>224</v>
+      </c>
+      <c r="G42">
+        <v>808</v>
+      </c>
+      <c r="H42">
+        <v>102</v>
+      </c>
+      <c r="I42">
+        <v>202</v>
+      </c>
+      <c r="J42">
+        <v>612</v>
+      </c>
+      <c r="K42">
+        <v>99</v>
+      </c>
+      <c r="L42">
+        <v>371</v>
+      </c>
+      <c r="M42">
+        <v>1171</v>
+      </c>
+      <c r="N42">
+        <v>72</v>
+      </c>
+      <c r="O42">
+        <v>105</v>
+      </c>
+      <c r="P42">
+        <v>591</v>
+      </c>
+      <c r="Q42">
+        <v>78</v>
+      </c>
+      <c r="R42">
+        <v>84</v>
+      </c>
+      <c r="S42">
+        <v>476</v>
+      </c>
+      <c r="T42">
+        <v>59</v>
+      </c>
+      <c r="U42">
+        <v>115</v>
+      </c>
+      <c r="V42">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="2">
+        <f>SUM(E43,H43,K43,N43,Q43,T43)</f>
+        <v>489</v>
+      </c>
+      <c r="C43">
+        <v>110</v>
+      </c>
+      <c r="D43">
+        <v>779</v>
+      </c>
+      <c r="E43">
+        <v>102</v>
+      </c>
+      <c r="F43">
+        <v>306</v>
+      </c>
+      <c r="G43">
+        <v>979</v>
+      </c>
+      <c r="H43">
+        <v>101</v>
+      </c>
+      <c r="I43">
+        <v>215</v>
+      </c>
+      <c r="J43">
+        <v>646</v>
+      </c>
+      <c r="K43">
+        <v>97</v>
+      </c>
+      <c r="L43">
+        <v>417</v>
+      </c>
+      <c r="M43">
+        <v>1244</v>
+      </c>
+      <c r="N43">
+        <v>76</v>
+      </c>
+      <c r="O43">
+        <v>68</v>
+      </c>
+      <c r="P43">
+        <v>448</v>
+      </c>
+      <c r="Q43">
+        <v>62</v>
+      </c>
+      <c r="R43">
+        <v>398</v>
+      </c>
+      <c r="S43">
+        <v>1196</v>
+      </c>
+      <c r="T43">
+        <v>51</v>
+      </c>
+      <c r="U43">
+        <v>263</v>
+      </c>
+      <c r="V43">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22">
+      <c r="A44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="2">
+        <f>SUM(E44,H44,K44,N44,Q44,T44)</f>
+        <v>514</v>
+      </c>
+      <c r="C44">
+        <v>140</v>
+      </c>
+      <c r="D44">
+        <v>840</v>
+      </c>
+      <c r="E44">
+        <v>106</v>
+      </c>
+      <c r="F44">
+        <v>152</v>
+      </c>
+      <c r="G44">
+        <v>642</v>
+      </c>
+      <c r="H44">
+        <v>93</v>
+      </c>
+      <c r="I44">
+        <v>325</v>
+      </c>
+      <c r="J44">
+        <v>910</v>
+      </c>
+      <c r="K44">
+        <v>111</v>
+      </c>
+      <c r="L44">
+        <v>167</v>
+      </c>
+      <c r="M44">
+        <v>707</v>
+      </c>
+      <c r="N44">
+        <v>63</v>
+      </c>
+      <c r="O44">
+        <v>270</v>
+      </c>
+      <c r="P44">
+        <v>944</v>
+      </c>
+      <c r="Q44">
+        <v>76</v>
+      </c>
+      <c r="R44">
+        <v>102</v>
+      </c>
+      <c r="S44">
+        <v>541</v>
+      </c>
+      <c r="T44">
+        <v>65</v>
+      </c>
+      <c r="U44">
+        <v>54</v>
+      </c>
+      <c r="V44">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22">
+      <c r="A45" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" s="2">
+        <f>SUM(E45,H45,K45,N45,Q45,T45)</f>
+        <v>529</v>
+      </c>
+      <c r="C45">
+        <v>95</v>
+      </c>
+      <c r="D45">
+        <v>737</v>
+      </c>
+      <c r="E45">
+        <v>106</v>
+      </c>
+      <c r="F45">
+        <v>152</v>
+      </c>
+      <c r="G45">
+        <v>642</v>
+      </c>
+      <c r="H45">
+        <v>83</v>
+      </c>
+      <c r="I45">
+        <v>471</v>
+      </c>
+      <c r="J45">
+        <v>1226</v>
+      </c>
+      <c r="K45">
+        <v>120</v>
+      </c>
+      <c r="L45">
+        <v>73</v>
+      </c>
+      <c r="M45">
+        <v>350</v>
+      </c>
+      <c r="N45">
+        <v>63</v>
+      </c>
+      <c r="O45">
+        <v>270</v>
+      </c>
+      <c r="P45">
+        <v>944</v>
+      </c>
+      <c r="Q45">
+        <v>84</v>
+      </c>
+      <c r="R45">
+        <v>22</v>
+      </c>
+      <c r="S45">
+        <v>215</v>
+      </c>
+      <c r="T45">
+        <v>73</v>
+      </c>
+      <c r="U45">
+        <v>13</v>
+      </c>
+      <c r="V45">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22">
+      <c r="A46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="2">
+        <f>SUM(E46,H46,K46,N46,Q46,T46)</f>
+        <v>485</v>
+      </c>
+      <c r="C46">
+        <v>110</v>
+      </c>
+      <c r="D46">
+        <v>779</v>
+      </c>
+      <c r="E46">
+        <v>98</v>
+      </c>
+      <c r="F46">
+        <v>455</v>
+      </c>
+      <c r="G46">
+        <v>1255</v>
+      </c>
+      <c r="H46">
+        <v>114</v>
+      </c>
+      <c r="I46">
+        <v>62</v>
+      </c>
+      <c r="J46">
+        <v>262</v>
+      </c>
+      <c r="K46">
+        <v>88</v>
+      </c>
+      <c r="L46">
+        <v>576</v>
+      </c>
+      <c r="M46">
+        <v>1470</v>
+      </c>
+      <c r="N46">
+        <v>72</v>
+      </c>
+      <c r="O46">
+        <v>105</v>
+      </c>
+      <c r="P46">
+        <v>591</v>
+      </c>
+      <c r="Q46">
+        <v>65</v>
+      </c>
+      <c r="R46">
+        <v>279</v>
+      </c>
+      <c r="S46">
+        <v>1002</v>
+      </c>
+      <c r="T46">
+        <v>48</v>
+      </c>
+      <c r="U46">
+        <v>323</v>
+      </c>
+      <c r="V46">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="2">
+        <f>SUM(E47,H47,K47,N47,Q47,T47)</f>
+        <v>495</v>
+      </c>
+      <c r="C47">
+        <v>360</v>
+      </c>
+      <c r="D47">
+        <v>1208</v>
+      </c>
+      <c r="E47">
+        <v>101</v>
+      </c>
+      <c r="F47">
+        <v>335</v>
+      </c>
+      <c r="G47">
+        <v>1041</v>
+      </c>
+      <c r="H47">
+        <v>96</v>
+      </c>
+      <c r="I47">
+        <v>280</v>
+      </c>
+      <c r="J47">
+        <v>816</v>
+      </c>
+      <c r="K47">
+        <v>98</v>
+      </c>
+      <c r="L47">
+        <v>386</v>
+      </c>
+      <c r="M47">
+        <v>1206</v>
+      </c>
+      <c r="N47">
+        <v>73</v>
+      </c>
+      <c r="O47">
+        <v>95</v>
+      </c>
+      <c r="P47">
+        <v>552</v>
+      </c>
+      <c r="Q47">
+        <v>75</v>
+      </c>
+      <c r="R47">
+        <v>129</v>
+      </c>
+      <c r="S47">
+        <v>638</v>
+      </c>
+      <c r="T47">
+        <v>52</v>
+      </c>
+      <c r="U47">
+        <v>192</v>
+      </c>
+      <c r="V47">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="2">
+        <f>SUM(E48,H48,K48,N48,Q48,T48)</f>
+        <v>495</v>
+      </c>
+      <c r="C48">
+        <v>124</v>
+      </c>
+      <c r="D48">
+        <v>813</v>
+      </c>
+      <c r="E48">
+        <v>103</v>
+      </c>
+      <c r="F48">
+        <v>258</v>
+      </c>
+      <c r="G48">
+        <v>882</v>
+      </c>
+      <c r="H48">
+        <v>114</v>
+      </c>
+      <c r="I48">
+        <v>62</v>
+      </c>
+      <c r="J48">
+        <v>262</v>
+      </c>
+      <c r="K48">
+        <v>93</v>
+      </c>
+      <c r="L48">
+        <v>485</v>
+      </c>
+      <c r="M48">
+        <v>1349</v>
+      </c>
+      <c r="N48">
+        <v>56</v>
+      </c>
+      <c r="O48">
+        <v>403</v>
+      </c>
+      <c r="P48">
+        <v>1205</v>
+      </c>
+      <c r="Q48">
+        <v>77</v>
+      </c>
+      <c r="R48">
+        <v>102</v>
+      </c>
+      <c r="S48">
+        <v>541</v>
+      </c>
+      <c r="T48">
+        <v>52</v>
+      </c>
+      <c r="U48">
+        <v>192</v>
+      </c>
+      <c r="V48">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22">
+      <c r="A49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" s="2">
+        <f>SUM(E49,H49,K49,N49,Q49,T49)</f>
+        <v>507</v>
+      </c>
+      <c r="C49">
+        <v>92</v>
+      </c>
+      <c r="D49">
+        <v>730</v>
+      </c>
+      <c r="E49">
+        <v>98</v>
+      </c>
+      <c r="F49">
+        <v>455</v>
+      </c>
+      <c r="G49">
+        <v>1255</v>
+      </c>
+      <c r="H49">
+        <v>99</v>
+      </c>
+      <c r="I49">
+        <v>241</v>
+      </c>
+      <c r="J49">
+        <v>710</v>
+      </c>
+      <c r="K49">
+        <v>76</v>
+      </c>
+      <c r="L49">
+        <v>744</v>
+      </c>
+      <c r="M49">
+        <v>1694</v>
+      </c>
+      <c r="N49">
+        <v>90</v>
+      </c>
+      <c r="O49">
+        <v>2</v>
+      </c>
+      <c r="P49">
+        <v>63</v>
+      </c>
+      <c r="Q49">
+        <v>81</v>
+      </c>
+      <c r="R49">
+        <v>38</v>
+      </c>
+      <c r="S49">
+        <v>306</v>
+      </c>
+      <c r="T49">
+        <v>63</v>
+      </c>
+      <c r="U49">
+        <v>73</v>
+      </c>
+      <c r="V49">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22">
+      <c r="A50" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" s="2">
+        <f>SUM(E50,H50,K50,N50,Q50,T50)</f>
+        <v>472</v>
+      </c>
+      <c r="C50">
+        <v>365</v>
+      </c>
+      <c r="D50">
+        <v>1214</v>
+      </c>
+      <c r="E50">
+        <v>100</v>
+      </c>
+      <c r="F50">
+        <v>367</v>
+      </c>
+      <c r="G50">
+        <v>1104</v>
+      </c>
+      <c r="H50">
+        <v>91</v>
+      </c>
+      <c r="I50">
+        <v>365</v>
+      </c>
+      <c r="J50">
+        <v>990</v>
+      </c>
+      <c r="K50">
+        <v>90</v>
+      </c>
+      <c r="L50">
+        <v>533</v>
+      </c>
+      <c r="M50">
+        <v>1417</v>
+      </c>
+      <c r="N50">
+        <v>69</v>
+      </c>
+      <c r="O50">
+        <v>146</v>
+      </c>
+      <c r="P50">
+        <v>695</v>
+      </c>
+      <c r="Q50">
+        <v>66</v>
+      </c>
+      <c r="R50">
+        <v>279</v>
+      </c>
+      <c r="S50">
+        <v>1002</v>
+      </c>
+      <c r="T50">
+        <v>56</v>
+      </c>
+      <c r="U50">
+        <v>151</v>
+      </c>
+      <c r="V50">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22">
+      <c r="A51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="2">
+        <f>SUM(E51,H51,K51,N51,Q51,T51)</f>
         <v>480</v>
       </c>
-      <c r="X51">
+      <c r="C51">
         <v>501</v>
       </c>
-      <c r="Y51">
+      <c r="D51">
         <v>1392</v>
       </c>
-      <c r="Z51">
+      <c r="E51">
         <v>80</v>
       </c>
-      <c r="AA51">
+      <c r="F51">
         <v>835</v>
       </c>
-      <c r="AB51">
+      <c r="G51">
         <v>1795</v>
       </c>
-      <c r="AC51">
+      <c r="H51">
         <v>109</v>
       </c>
-      <c r="AD51">
+      <c r="I51">
         <v>114</v>
       </c>
-      <c r="AE51">
+      <c r="J51">
         <v>388</v>
       </c>
-      <c r="AF51">
+      <c r="K51">
         <v>103</v>
       </c>
-      <c r="AG51">
+      <c r="L51">
         <v>302</v>
       </c>
-      <c r="AH51">
+      <c r="M51">
         <v>1023</v>
       </c>
-      <c r="AI51">
+      <c r="N51">
         <v>57</v>
       </c>
-      <c r="AJ51">
+      <c r="O51">
         <v>377</v>
       </c>
-      <c r="AK51">
+      <c r="P51">
         <v>1165</v>
       </c>
-      <c r="AL51">
+      <c r="Q51">
         <v>81</v>
       </c>
-      <c r="AM51">
+      <c r="R51">
         <v>38</v>
       </c>
-      <c r="AN51">
+      <c r="S51">
         <v>306</v>
       </c>
-      <c r="AO51">
+      <c r="T51">
         <v>50</v>
       </c>
-      <c r="AP51">
+      <c r="U51">
         <v>263</v>
       </c>
-      <c r="AQ51">
+      <c r="V51">
         <v>1034</v>
       </c>
     </row>
@@ -7540,6 +7826,6 @@
   <conditionalFormatting sqref="A2:A51">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>